--- a/Ministry_of_Industry.xlsx
+++ b/Ministry_of_Industry.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E120"/>
+  <dimension ref="A1:E139"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
   <cols>
     <col width="45" customWidth="1" min="1" max="1"/>
@@ -5076,6 +5076,806 @@
         </is>
       </c>
     </row>
+    <row r="121">
+      <c r="A121" t="inlineStr">
+        <is>
+          <t>عيسى الخوري يبحث مع قيادات رجال الأعمال الفرنسيين تعزيز الاستثمارات الصناعية في لبنان</t>
+        </is>
+      </c>
+      <c r="B121" t="inlineStr">
+        <is>
+          <t>http://www.industry.gov.lb/Media/News/عيسى-الخوري-يبحث-مع-قيادات-رجال-الاعمال-الفرنسيين</t>
+        </is>
+      </c>
+      <c r="C121" t="inlineStr">
+        <is>
+          <t>2011-01-01</t>
+        </is>
+      </c>
+      <c r="D121" t="inlineStr">
+        <is>
+          <t>عيسى الخوري يبحث مع قيادات رجال الأعمال الفرنسيين تعزيز الاستثمارات الصناعية في لبنان
+في إطار الجهود الرامية إلى استقطاب الاستثمارات الأجنبية وتعزيز الشراكات الصناعية الدولية، عقد وزير الصناعة جو عيسى الخوري في حضور سفير لبنان في فرنسا والوفد المرافق، سلسلة لقاءات في العاصمة الفرنسية باريس مع قيادات بارزة في مجتمع الأعمال الفرنسي.
+وفي هذا السياق، اجتمع الوزير عيسى الخوري مع رئيس تجمّع المؤسسات الفرنسية (MEDEF) باتريك مارتان، وتضم أكثر من 240 ألف مؤسسة من مختلف القطاعات الانتاجية.
+وتركّزت المباحثات على سبل تعزيز التعاون الصناعي بين لبنان وفرنسا، واستقطاب استثمارات فرنسية جديدة، لا سيما في الصناعات التكنولوجية، من خلال إقامة شراكات إنتاجية والاستفادة من الكفاءات الهندسية والتقنية اللبنانية.
+كما تناول البحث إمكان اعتماد نماذج التعاون الصناعي العابر للحدود، بما فيها الـNearshoring والـOffshoring، بهدف تمكين الشركات الفرنسية من توسيع قدراتها الإنتاجية وتطوير أنشطتها في لبنان، ودمج المؤسسات الصناعية اللبنانية في سلاسل الإنتاج العالمية.
+وأكد الوزير عيسى الخوري أن لبنان يمتلك مقوّمات تؤهّله ليكون شريكاً صناعياً وتكنولوجياً للشركات الفرنسية، بفضل كفاءاته البشرية وخبراته الصناعية وقدرته على تقديم حلول إنتاجية تنافسية ذات قيمة مضافة عالية.
+ووجّه الوزير دعوة إلى السيد مارتان لزيارة لبنان خلال شهر كانون الثاني المقبل، على رأس وفد من الصناعيين ورجال الأعمال الفرنسيين، للاطلاع على الفرص الاستثمارية المتاحة وإمكانات إقامة شراكات مباشرة مع المؤسسات الصناعية اللبنانية.
+كذلك جرى البحث في تنظيم منتدى للاستثمار الصناعي اللبناني في باريس، يجمع مستثمرين وشركات فرنسية مع صناعيين لبنانيين لعرض مشاريع وفرص استثمارية محدّدة، على أن تتولّى لجنة مشتركة التحضير لهذا الحدث ومتابعة نتائج اللقاءات.
+وفي السياق نفسه، اجتمع الوزير عيسى الخوري مع الرئيس الفخري لـMEDEF والرئيس الفخري لتحالف أرباب العمل الفرنكوفونيين جوفروا دو بيزيو، و تناول اللقاء فرص توسيع شبكة العلاقات الاقتصادية والصناعية للبنان مع مجتمع الأعمال الفرنسي والفرنكوفوني.
+وتندرج هذه اللقاءات ضمن توجّه وزارة الصناعة الهادف إلى تعزيز موقع لبنان كمركز للإنتاج الصناعي المتخصص والابتكار التكنولوجي، وجذب الاستثمارات التي تساهم في خلق فرص عمل نوعية، وزيادة الصادرات، ورفع القيمة المضافة للصناعة اللبنانية.</t>
+        </is>
+      </c>
+      <c r="E121" t="inlineStr">
+        <is>
+          <t>2026-10-29T11:21:19.235180+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="inlineStr">
+        <is>
+          <t>مناقشات في السفارة اللبنانية في باريس لتسهيل انسياب السلع الى اوروبا عيسى الخوري:"الشراكة بين القطاع</t>
+        </is>
+      </c>
+      <c r="B122" t="inlineStr">
+        <is>
+          <t>http://www.industry.gov.lb/Media/News/مناقشات-في-السفارة-اللبنانية-في-باريس-لتسهيل-انسيا</t>
+        </is>
+      </c>
+      <c r="C122" t="inlineStr">
+        <is>
+          <t>2011-01-01</t>
+        </is>
+      </c>
+      <c r="D122" t="inlineStr">
+        <is>
+          <t>مناقشات في السفارة اللبنانية في باريس لتسهيل انسياب السلع الى اوروبا عيسى الخوري:"الشراكة بين القطاعين العام والخاص وقوّة الاغتراب تغعّل الاقتصاد والاستثمار"
+واصل وزير الصناعة جو عيسى الخوري زيارته الرسمية الى فرنسا، حيث تفقّد العارضين في الجناح اللبناني في معرض سيال ٢٠٢٦ المخصّص للصناعات الغذائية. والتقى كل صناعي عارض واستمع إلى طلباتهم والتحدّيات التي يواجهونها. وأثنى على نجاحاتهم وتفوّقهم في تصدير منتجاتهم.
+لقاء في السفارة
+وقد ترأس الوزير عيسى الخوري اجتماع عمل دعا إليه السفير ربيع الشاعر في مقرّ السفارة اللبنانية في باريس.
+وحضر الاجتماع المدراء العامون لوزارات الصناعة والزراعة والاقتصاد والتجارة اضافة الى رئيس نقابة اصحاب الصناعات الغذائية في لبنان.
+وهدفت المناقشات إلى التنسيق بين الوزارات من اجل تسهيل سبل انسياب البضائع اللبنانية الى فرنسا وأوروبا عموماً، مع وجوب حسن تطبيق اتفاقية الشراكة بين لبنان والاتحاد الاوروبي، بما يتيح رفع نسبة الصادرات اللبنانية الى القارة الأوروبية.</t>
+        </is>
+      </c>
+      <c r="E122" t="inlineStr">
+        <is>
+          <t>2026-10-29T11:21:21.764439+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="inlineStr">
+        <is>
+          <t>الشاعر كرّم عيسى الخوري في السفارة اللبنانية في فرنسا وزير الصناعة:" المنطقة تتّجه نحو السلام والقط</t>
+        </is>
+      </c>
+      <c r="B123" t="inlineStr">
+        <is>
+          <t>http://www.industry.gov.lb/Media/News/الشاعر-كرم-عيسى-الخوري-في-السفارة-اللبنانية-في-فرن</t>
+        </is>
+      </c>
+      <c r="C123" t="inlineStr">
+        <is>
+          <t>2011-01-01</t>
+        </is>
+      </c>
+      <c r="D123" t="inlineStr">
+        <is>
+          <t>الشاعر كرّم عيسى الخوري في السفارة اللبنانية في فرنسا وزير الصناعة:" المنطقة تتّجه نحو السلام والقطاع الخاص يحتاج الى الاستثمارات"
+أكد وزير الصناعة جو عيسى الخوري أن "لبنان طائرٌ يحلّق بجناحين: جناحٌ مقيم، والثاني غير مقيم منتشر في مختلف أنحاء العالم". وأشار إلى أهمية التواصل الدائم مع اللبنانيين المنتشرين، الذين دفعتهم الأزمات والحروب والظروف الاقتصادية الصعبة إلى مغادرة وطنهم.
+وأستحضر مقولةً تعبّر عن هذه العلاقة المميّزة: يمكن إخراج اللبناني من لبنان، لكن لا يمكن إخراج لبنان من قلب اللبناني، لافتا الى أن لبنان يبقى راسخًا في وجدان كل لبناني، حتى وإن وُلد وعاش خارج أرض الوطن.
+كلام الوزير عيسى الخوري جاء خلال حفل استقبال أُقامه السفير اللبناني في فرنسا ربيع الشاعر على شرفه في مقرّ السفارة اللبنانية في باريس في حضور عدد من أبناء الجالية والمشاركين في معرض سيال الدولي للصناعات الغذائية والعرق المشروبات الروحية.
+وأكد أنه "حان الوقت للانتهاء من الحروب، فالمنطقة متّجهة نحو السلام، على الرغم من الظروف الصعبة التي نعيشها". وأضاف: "قد يكون الطريق إلى السلام محفوفًا بالحروب، لكنه سيتحقق في النهاية. من هنا، أدعوكم إلى الاستعداد للمرحلة المقبلة، وإلى أن تكونوا شركاء فاعلين في الاستثمار في لبنان والمساهمة في نهوضه الاقتصادي".
+ودعا الئ وجوب "التمييز بين الدولة اللبنانية والقطاع الخاص. فالدولة تواجه تحديات كبيرة، في مقدّمها الديون والمشاكل الاقتصادية والمالية، وهي تحتاج إلى مساعدات خارجية، أمّا القطاع الخاص، فلا يحتاج إلّا إلى الاستثمارات والمستثمرين، وهذا هو الفارق الأساسي".
+ولفت إلى أن تاريخ لبنان أثبت أن القطاع الخاص هو من حقّق الازدهار الاقتصادي، ولطالما طالب الدولة،أي القطاع الخاص، بأن تتيح له العمل، وأن تقوم بدورها في التشريع ووضع الأطر التنظيمية السليمة التي تسمح للمؤسسات بالنمو والمنافسة".
+وشدّد على أن المطلوب اليوم هو تعزيز قدرات القطاع الخاص، إذ إن معالجة التحديات التي تواجه الدولة تحتاج إلى وقت، فيما يستطيع القطاع الخاص أن يشكّل رافعة أساسية للنهوض الاقتصادي من خلال استقطاب الاستثمارات."
+في هذا الإطار، أشار إلى تغيّر في أسلوب تعاطي معظم الوزراء مع الإدارة، نظرًا إلى انتمائهم إلى القطاع الخاص، ويعملون، من خلال المشاورات واللقاءات مع الجهات المعنية في الخارج، على استكشاف فرص التعاون والشراكة التي من شأنها دعم القطاع الخاص اللبناني.
+أمّا للصناعيين اللبنانيين، ولا سيّما المصدّرين منهم، فقال: "إنّكم في صفوف المقاومين الحقيقيين، لأنّكم لا تزالون تنتجون وتصدّرون"، مشيرًا إلى مساهمتهم في إدخال أكثر من 3 مليارات دولار سنويًا من العملات الأجنبية إلى لبنان عبر التصدير.
+وأوضح أن سبب المشكلة في الاقتصاد اللبناني يبقى العجز في الميزان التجاري، الذي يُقدّر بنحو 17 مليار دولار سنويًا. ففي العام الماضي، بلغت قيمة الواردات نحو 21 مليار دولار، في حين لم تتجاوز الصادرات نحو 3.5 مليارات دولار، ما يعكس فجوة كبيرة لا يمكن الاستمرار في تجاهلها.
+لذلك، أكّد ضرورة العمل على مسارين متوازيين: الأول، زيادة الإنتاج الصناعي، وتحديدًا إنتاج البدائل القادرة على الحلول مكان جزء من السلع المستوردة؛ والثاني، فتح أسواق جديدة أمام الصناعيين اللبنانيين.
+وفي هذا الإطار، كشف أنه أعدّ دراسة متخصّصة ممولة من الاتحاد الأوروبي شارفت على الانتهاء، تتناول الأسواق العالمية التي تهمّ المنتجات اللبنانية، على أن توضع نتائجها قريبًا في تصرّف جمعية الصناعيين اللبنانيين، بما يتيح للصناعيين الاستفادة منها.
+وفي الختام، توجّه بالشكر إلى السفير الشاعر، على جهوده في تعزيز العلاقات اللبنانية الفرنسية والعمل مع فرنسا لتقديم المساعدة للبنان، فضلًا عن دوره في جمع اللبنانيين في فرنسا وتعزيز الروابط فيما بينهم.
+السفير الشاعر
+وأشار الشاعر إلى أن مشاركة 37 شركة لبنانية في معرض SIAL تؤكد حضور لبنان وصناعاته، ولا سيّما الصناعات الغذائية الطموحة في المعارض الدولية. واعتبر أن هؤلاء الصناعيين هم السفراء الغذائيون للبنان، ويمثّلون الدبلوماسية الغذائية التي تسير بالتوازي مع الدبلوماسية السياسية، وتُدخل لبنان إلى كل منزل.
+ولفت إلى أن المنتجات اللبنانية "بتكبّر القلب"، لما تتميّز به من جودة وابتكار، متوقفًا عند عدد من المنتجات اللبنانية التي حازت جوائز في دورات سابقة من معرض SIAL، ما يؤكد قدرة رائد الأعمال اللبناني على الإبداع رغم كل الصعوبات.
+وأوضح أن التبادل التجاري بين لبنان وفرنسا يبلغ نحو 100 مليون يورو، فيما لا تتجاوز حصة لبنان منه 14 مليون يورو. وشدّد على ضرورة السعي إلى تحسين تطبيق اتفاقية الشراكة بين لبنان وفرنسا، التي تسهّل دخول المنتجات الزراعية والغذائية إلى الأسواق الفرنسية والأوروبية. وأشار إلى أن فرنسا تمثّل سوقًا كبيرة وواعدة، إذ تبلغ الاستثمارات في الصناعات الغذائية فيها نحو 100 مليار يورو، ما يجعلها محطة أساسية للوصول إلى الأسواق الأوروبية.
+وأضاف أن وجود ممثّلي وزارات الصناعة والاقتصاد والتجارة والزراعة، ستتيح للسفارة الاطلاع على سبل تعزيز التواصل بين الصناعيين اللبنانيين والمستهلك الفرنسي.
+كما تحدّث عن لقاء سيُنظّم بين المصنّعين اللبنانيين والمستهلكين الفرنسيين، معلنًا عن تواصل قريب عبر الإنترنت مع التجار والصناعيين اللبنانيين، بهدف فهم احتياجاتهم وإبراز سبل الدعم التي يمكن أن تقدّمها السفارة اللبنانية في فرنسا. وأكد أن السفارة ستسعى، رغم محدودية إمكاناتها، إلى التعاون مع اللبنانيين في فرنسا لتوفير الدعم اللازم.
+بو نادر
+كما تحدث الأمين العام لغرفة التجارة الفرنسية-اللبنانية داني ابي شهلا، رئيس نقابة أصحاب الصناعات الغذائية اللبنانية رامز بو نادر الذي سلّم ورئيسة شركة هوسبيتاليتي سيرفسز جومانا دموس سلامة درعاً تكريمياً الى السفير الشاعر.</t>
+        </is>
+      </c>
+      <c r="E123" t="inlineStr">
+        <is>
+          <t>2026-10-29T11:21:24.258026+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="inlineStr">
+        <is>
+          <t>عيسى الخوري افتتح الجناح اللبناني في معرض سيال الدولي في باريس " صناعاتنا الغذائية فنّ وذوق وابداع و</t>
+        </is>
+      </c>
+      <c r="B124" t="inlineStr">
+        <is>
+          <t>http://www.industry.gov.lb/Media/News/عيسى-الخوري-افتتح-الجناح-اللبناني-في-معرض-سيال-الد</t>
+        </is>
+      </c>
+      <c r="C124" t="inlineStr">
+        <is>
+          <t>2011-01-01</t>
+        </is>
+      </c>
+      <c r="D124" t="inlineStr">
+        <is>
+          <t>عيسى الخوري افتتح الجناح اللبناني في معرض سيال الدولي في باريس " صناعاتنا الغذائية فنّ وذوق وابداع ومنتشرة في مختلف الأسواق العالمية"
+افتتح وزير الصناعة جو عيسى الخوري الجناح اللبناني في معرض الغذاء والمشروبات الدولي SIAL 2026 في باريس، أحد أبرز المعارض العالمية المتخصصة في الصناعات الغذائية، بحضور السفير اللبناني في باريس ربيع الشاعر، و المدراء العامين لوزارات الصناعة عادل الشباب، الزراعة لويس لحود، والاقتصاد والتجارة محمد أبو حيدر، رئيس نقابة أصحاب الصناعات الغذائية اللبنانية رامز بو نادر, وبمشاركة صناعيين لبنانيين يسعون إلى تعزيز حضور المنتجات اللبنانية في الأسواق العالمية، وإبراز جودة الصناعة الغذائية اللبنانية وقدرتهم على المنافسة. علماً ان النقابة نظّمت الجناح بالتنسيق مع شركة هوسبيتاليتي سيرفسز.
+وأعرب عيسى الخوري خلال الافتتاح عن اعتزازه بمشاركة الصناعيين اللبنانيين في هذا المعرض العالمي، داعيًا إياهم إلى الفخر بما يحققونه من إنجازات، لا سيما أنهم يحملون اسم لبنان عالياً إلى الخارج ويقدّمون الصورة المشرقة عن لبنان، على الرغم من الأزمات والحروب وارتفاع كلفة الإنتاج وسائر التحديات التي تواجههم.
+وأكد أن الصناعيين اللبنانيين، لا سيما العاملين منهم في قطاع الصناعات الزراعية والغذائية، هم "مقاومون حقيقيون"، إذ يواصلون الإنتاج والاستثمار والتصدير ويتمسكون بمؤسساتهم، مشيدًا بصمودهم وإصرارهم على الحفاظ على الصناعة الوطنية وتطويرها.
+وأضاف: "انتم تصدرون الصناعات المميزة في لبنان، وهي الصناعات الغذائية. وقد اكتشف العالم المذاق اللذيذ لمطابخ البحر المتوسط فيما برز أكثر فأكثر المطبخ اللبناني كالاول بينهم. هذا التميّز لا يقتصر فقط على انتشار المطاعم اللبنانية في الخارج، بل يعود أيضًا إلى جهود مصدّري الصناعات العذائية الذين يعملون على إيصال المأكولات اللبنانية إلى كل منزل في أوروبا والولايات المتحدة الاميركية والخليج العربي وسائر دول العالم".
+وشدّد عيسى الخوري على أن لبنان، وإن كان لا يستطيع منافسة الدول الكبرى من حيث كميات الإنتاج، إلّا انه ينجح في المنافسة من حيث الجودة والنوعية، داعياً الى ضرورة المحافظة على هذا المستوى للمنتجات اللبنانية وتعزيز جودتها، ما يرسّخ حضورها في الأسواق الخارجية.
+كما لفت إلى أن التصدير يشكّل ركيزة أساسية لدعم الاقتصاد الوطني، إذ يساهم في إدخال العملات الأجنبية إلى البلاد وخلق فرص عمل جديدة وتثبيت اللبنانيين في وطنهم والحد من هجرتهم، مؤكّدا ان الوقت قد حان للتوقف عن تصدير طاقات لبنان البشرية، والعمل بدلًا من ذلك على المحافظة عليهم في لبنان.
+وأوضح أنه من واجب الدولة والوزراء دعم القطاع الخاص ومواكبة احتياجاته، لأن دور الدولة، يتمثل في وضع الأطر المناسبة وتوفير الظروف التي تساعد القطاع الخاص على النمو والتطور.
+وختم متوجّها بالشكر الى صناعيي لبنان، ولا سيما أصحاب الصناعات الزراعية والغذائية، على جهودهم في الحفاظ على الإنتاج الوطني وتعزيز الصادرات، ومساهمتهم في إبراز الصورة الأجمل عن لبنان وتعزيز حضوره في الأسواق العالمية.
+بو نادر
+وألقى بو نادر كلمة:"اكد قيها أن "مشاركة النقابة وعدد من الصناعيين في معرض سيال الدولي في فرنسا للصناعات الغذائية والمشروبات، يثبت مرة جديدة تصميم الصناعيين اللبنانيين على قدراتهم ونجاحاتهم في عالم الغذاء، وهذا ما دفع وزير الصناعة الى المجيء الى باريس لافتتاح الجناح اللبناني بمشاركة زملاء في القطاع يمثّلون صناعات غذائية ونبيذ ومشروبات روحية ومشروبات أخرى متنوعة.
+لقد دأبت النقابة منذ ثلاثين سنة على نظيم الجناح اللبناني في أهم المعارض الدولية وقد نظّمت هذا العام الجناح اللبناني في معرض سيال ٢٠٢٦،وكان الافتتاح ناجحاً في حضور اعلام لبناني وأجنبي، وقد أبدوا اهتمامهم بالجناح اللبناني، مما يعكس تجاوب الرأي العام العربي والغربي مع مكونات المنتجات والمطبخ اللبناني.
+ليس بجديد مشاركة نقابتنا في اهم المعارض الدولية المتخصصة، وبينها غولف فود في دبي، وانوغا في المانيا، وسيال في باريس. هذه المشاركة تأتي من ارث وتاريخ وعراقة مصنّعينا الذين جعلوا من القطاع في طليعة القطاعات المصدّرة ويستحوذ على نسبة تقارب الخمسة وعشرين بالماية تقريباً من حجم الانتاج اللبناني المُصدّر.
+نحن مصمّمون على المضي قدماً بتطوير مصانعنا وتحديث خبراتنا والاطلاع على المهارات العالمية، بغية تقديم منتجاتنا بالشكل الأفضل في ظلّ التنافسية الحادة التي يشهدها العالم. كما نحن مستعدون لتبادل ابداعاتنا والفنّ والمهارة والذوق اللبناني لنتقرّب من العالم ولنقرّب العالم إلينا."</t>
+        </is>
+      </c>
+      <c r="E124" t="inlineStr">
+        <is>
+          <t>2026-10-29T11:21:26.948022+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="inlineStr">
+        <is>
+          <t>عيسى الخوري بحث مع تجمّع صناعيّي الضاحية الجنوبيّة أوضاع المصانع والتسهيلات الممكنة للمعامل المتضرّ</t>
+        </is>
+      </c>
+      <c r="B125" t="inlineStr">
+        <is>
+          <t>http://www.industry.gov.lb/Media/News/عيسى-الخوري-بحث-مع-تجمع-صناعيي-الضاحية-الجنوبية-او</t>
+        </is>
+      </c>
+      <c r="C125" t="inlineStr">
+        <is>
+          <t>2011-01-01</t>
+        </is>
+      </c>
+      <c r="D125" t="inlineStr">
+        <is>
+          <t>عيسى الخوري بحث مع تجمّع صناعيّي الضاحية الجنوبيّة أوضاع المصانع والتسهيلات الممكنة للمعامل المتضرّرة
+استقبل وزير الصناعة المهندس جو عيسى الخوري، في مكتبه بالوزارة في حضور مدير عام الصناعة عادل الشباب، رئيس تجمع صناعيّي الضاحية الجنوبية أحمد حسين الموسوي وأعضاء الهيئة الإدارية للتجمّع، وتمّ البحث في واقع القطاع الصناعي في الضاحية الجنوبية والتحديات التي تواجه المؤسسات، والعمل على تدعيم قدراتها الانتاجية.
+وتطرّق المجتمعون إلى أوضاع المصانع المتضررة فأكد الوزير أنه يولي هذا الموضوع الأهمية.
+وأثنى على جهود الصناعيّين وصمودهم والتزامهم بالاستمرار في العمل الصناعي مهما كانت التحديات.</t>
+        </is>
+      </c>
+      <c r="E125" t="inlineStr">
+        <is>
+          <t>2026-10-29T11:21:29.414197+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="inlineStr">
+        <is>
+          <t>"الصناعة" دعت المعاصر إلى التخلّص من جفت وزيبار معاصر الزيتون بطريقة سليمة تحت طائلة الإقفال</t>
+        </is>
+      </c>
+      <c r="B126" t="inlineStr">
+        <is>
+          <t>http://www.industry.gov.lb/Media/News/الصناعة-دعت-المعاصر-الى-التخلص-من-جفت-وزيبار-معاصر</t>
+        </is>
+      </c>
+      <c r="C126" t="inlineStr">
+        <is>
+          <t>2011-01-01</t>
+        </is>
+      </c>
+      <c r="D126" t="inlineStr">
+        <is>
+          <t>"الصناعة" دعت المعاصر إلى التخلّص من جفت وزيبار معاصر الزيتون بطريقة سليمة تحت طائلة الإقفال
+وطنية - أصدر وزير الصناعة جو عيسى الخوري القرار رقم ٨٠/١، دعا فيه معاصر الزيتون المرخّصة وفقاً للأصول إلى:
+١- تجميع الزيبار في خزانات ذات سعة تتناسب مع الكمية الناتجة خلال أسبوع عمل كحد أدنى وعدم رميه في الطبيعة أو الأنهر أو المجاري المائية أو الآبار الإرتوازية والتخلص أو إعادة إستعمال الزيبار بطريقة سليمة بيئياً.
+٢- تجميع الجفت في غرفة مستقلة داخل المؤسسة وتأمين تهوئة كافية منعاً لإنتشار الروائح وتسليمه للجهات المختصة والمرخص لها قانوناً بإعادة إستعماله أو تدويره أو تصنيعه. وذلك تحت طائلة الإقفال في حال عدم الإلتزام.
+المادة الثانية: يُبلغ هذا القرار من يلزم".</t>
+        </is>
+      </c>
+      <c r="E126" t="inlineStr">
+        <is>
+          <t>2026-10-29T11:21:31.977887+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="inlineStr">
+        <is>
+          <t>عيسى الخوري ممثلاً رئيس الحكومة في افتتاح معرض Project Lebanon : "إعادة الإعمار فرصة للصناعة لا عبئا</t>
+        </is>
+      </c>
+      <c r="B127" t="inlineStr">
+        <is>
+          <t>http://www.industry.gov.lb/Media/News/عيسى-الخوري-ممثلا-رييس-الحكومة-في-افتتاح-معرض-Proj</t>
+        </is>
+      </c>
+      <c r="C127" t="inlineStr">
+        <is>
+          <t>2011-01-01</t>
+        </is>
+      </c>
+      <c r="D127" t="inlineStr">
+        <is>
+          <t>عيسى الخوري ممثلاً رئيس الحكومة في افتتاح معرض Project Lebanon : "إعادة الإعمار فرصة للصناعة لا عبئاً على الميزان التجاري"
+مثّل وزير الصناعة جو عيسى الخوري رئيس مجلس الوزراء نواف سلام في افتتاح الدورة السابعة والعشرين من معرض Project Lebanon، الذي تنظمه الشركة الدولية للمعارض (IFP)، بحضور حشد من الشخصيات الرسمية والاقتصادية والصناعية، ومشاركة أكثر من 200 عارض.
+ورأى عيسى الخوري أن "تنظيم هذا المعرض اليوم يأتي في مرحلة مفصلية بالنسبة إلى لبنان، إذ لم تعد إعادة الإعمار مجرد قطاع اقتصادي، بل أصبحت أولوية وطنية، في ظل وجود عدد كبير من القرى والمدن المتعطّشة لاستعادة الحياة والنهوض من جديد، وهي تحتاج إلى إعادة إعمار وتحديث بنيتها التحتية، من شبكات الكهرباء والمياه والاتصالات إلى الطاقة الشمسية وسائر القطاعات الحيوية".
+وتابع: "عندما يلتقي أكثر من 200 عارض في لبنان، فإن ذلك يحمل رسالة واضحة يوجهها لبنان إلى الداخل والخارج، يؤكد من خلالها أنه جاهز لتوفير الفرص ومستعد لاستقبال الاستثمارات. كما أن ذلك يدل على أن العالم حاضر ليكون شريكاً في مسيرة إعادة الإعمار والاستثمار في لبنان".
+وشدد عيسى الخوري على ضرورة أن تشكل مرحلة إعادة الإعمار فرصة حقيقية للصناعة اللبنانية، لا عبئاً إضافياً على الميزان التجاري، مجددا التأكيد أن كل منتج يُصنع في لبنان ويُباع داخل السوق اللبناني يساهم في خلق فرص عمل جديدة للشباب، ويعزز قدرتهم على البقاء والعمل في لبنان، وهم الميزة التفاضلية الأساسية للإقتصاد اللبناني".
+وهنّأ عيسى الخوري IFP ورئيس مجلس إدارتها ومديرها العام ألبير عون على تنظيم هذا المعرض بنسخته السابعة والعشرين مشيداً بالاستمرارية والجهد اللذين يبذلهما في سبيل دعم مسيرة إعادة الإعمار في لبنان ودعم القطاعات الاقتصادية اللبنانية.</t>
+        </is>
+      </c>
+      <c r="E127" t="inlineStr">
+        <is>
+          <t>2026-10-29T11:21:34.557889+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="inlineStr">
+        <is>
+          <t>عيسى الخوري أنجز سابقة لم تتحقق منذ ١٥ عاماً: تعيين أحد عشر رئيس مصلحة أصيلين في وزارة الصناعة</t>
+        </is>
+      </c>
+      <c r="B128" t="inlineStr">
+        <is>
+          <t>http://www.industry.gov.lb/Media/News/عيسى-الخوري-انجز-سابقة-لم-تتحقق-منذ-١٥-عاما-تعيين</t>
+        </is>
+      </c>
+      <c r="C128" t="inlineStr">
+        <is>
+          <t>2011-01-01</t>
+        </is>
+      </c>
+      <c r="D128" t="inlineStr">
+        <is>
+          <t>عيسى الخوري أنجز سابقة لم تتحقق منذ ١٥ عاماً: تعيين أحد عشر رئيس مصلحة أصيلين في وزارة الصناعة
+أصدرت وزارة الصناعة البيان التالي:"بعد مرور أكثر من خمسة عشر عاماً على شغور وظائف الفئة الثانية في ملاك وزارة الصناعة التي كانت معيّنة بالوكالة طيلة هذه السنوات، مع ما يرافق هذا الفراغ من خلل داخل الادارة على صعيد عدم تكامل الآداء مع المهام والدور، رغم قيام الموظّفين المعيّنين موقّتاً بواجباتهم الوظيفيّة بما أدّى الى تلبيتهم مطالب كلّ من القطاعَين العام والخاص والمواطن والصناعي، وأمّنوا الخدمات اللازمة لتسيير المرفق العام.
+ومنذ تسلّم حقيبة الصناعة، انكبّ الوزير عيسى الخوري على معالجة هذا الملف برويّة ولكن بحزم ومثابرة، انطلاقاً من قناعته بأن التعيينات في الملاك اجراء قانوني واداري واجب وضروري وأساسي تكتمل معه هيكليّة الادارة في وظائف الفئة الثانية في الوزارة. وتابع الملف مع رئاسة الجمهورية ورئاسة الحكومة ومجلس الخدمة المدنية وسائر الهيئات حتى سلكت مجراها القانوني.
+ويؤكد وزير الصناعة أنّ هذا الإنجاز الذي تحقّق سابقة لم تحدث منذ أكثر من خمسة عشر عاماً، وهو يهنّى المعيّنين على كفاءتهم وجدارتهم واستحقاقهم هذه المناصب، متمنّياً لهم التوفيق والمباشرة بالعمل بكلّ نشاط واندفاع من أجل خدمة الاقتصاد والصناعة والمواطن.
+وشكر وزير الصناعة رئيس الجمهورية العماد جوزاف عون ورئيس مجلس الوزراء الدكتور نواف سلام ووزير المالية الأستاذ ياسين جابر على توقيعهم المرسوم."
+أسماء المعيّنين وتوزيعهم على المصالح
+وفي ما يلي أسماء المعيّنين والمصالح التي عُيّنوا فيها:
+- ذيب محمد هاشم: رئيس مصلحة الصناعة الاقليمية في النبطية
+- مروان متى جوهر: رئيس مصلحة التراخيص الصناعية
+- جمانا ميشال الهاشم: رئيسة مصلحة الديوان
+- هبة نجم الدين شحادة: رئيسة مصلحة الدراسات الاقتصادية والانماء الصناعي
+- لينا حسين عاصي: رئيسة مصلحة الشؤون التقنية والخدمات الصناعية
+- جمانة مدرك الصيادي: رئيسة مصلحة الصناعة الاقليمية في الشمال
+- مأمون محمد ناصر: رئيس مصلحة الصناعة الاقليمية في بعلبك-الهرمل
+- بيار انطوان عمران: رئيس مصلحة الصناعة الاقليمية في البقاع
+- ديفيد هنري واكيم: رئيس مصلحة الصناعة الاقليمية في الجنوب
+- شارل جرجس العبود: رئيس مصلحة الصناعة الاقليمية في عكار
+- علاء الدين عمر الحجار: رئيس مصلحة المعلومات الصناعية.
+ــــــــــــــــــــــــــــــ</t>
+        </is>
+      </c>
+      <c r="E128" t="inlineStr">
+        <is>
+          <t>2026-10-29T11:21:37.140726+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="inlineStr">
+        <is>
+          <t>رعى وزير الصناعة المهندس جو عيسى الخوري حفل افتتاح معرض "صنع في البقاع" في بارك جوزيف طعمة سكاف - زح</t>
+        </is>
+      </c>
+      <c r="B129" t="inlineStr">
+        <is>
+          <t>http://www.industry.gov.lb/Media/News/رعى-وزير-الصناعة-المهندس-جو-عيسى-الخوري-حفل-افتتاح</t>
+        </is>
+      </c>
+      <c r="C129" t="inlineStr">
+        <is>
+          <t>2011-01-01</t>
+        </is>
+      </c>
+      <c r="D129" t="inlineStr">
+        <is>
+          <t>رعى وزير الصناعة المهندس جو عيسى الخوري حفل افتتاح معرض "صنع في البقاع" في بارك جوزيف طعمة سكاف - زحلة، والذي نظمته غرفة التجارة والصناعة والزراعة في زحلة والبقاع بالشراكة مع تجمع الصناعيين في البقاع وبلدية زحلة – المعلقة وتعنايل.
+وحضر الحفل وزير الاقتصاد والتجارة الدكتور عامر البساط، وزير العمل الدكتور محمد حيدر، وزير الزراعة الدكتور نزار الهاني ممثلاً بمدير عام وزارة الزراعة المهندس لويس لحود، ووزير الإعلام الدكتور بول مرقص ممثلاً بمنسقة مكتب زحلة في الوكالة الوطنية للإعلام ماريان الحاج، النائبان جورج عقيص وياسين ياسين، محافظ البقاع القاضي كمال أبو جوده،سفير المملكة العربية السعودية في لبنان فهد الدوسري ممثلاً بالملحق التجاري في السفارة زايد الأسمري، سفير كولومبيا في لبنان Edwin Alfonso، سفير المكسيك فرانسيسكو ارنستو روميرو بوك، رئيس المجلس الأعلى للجمارك العميد مصباح الخليل، ووزراء ونواب سابقون، رئيس تجمع الصناعيين في البقاع نقولا أبو فيصل، رئيس الهيئات الاقتصادية الوزير السابق محمد شقير، رئيس غرفة التجارة والصناعة والزراعة في طرابلس والشمال توفيق دبوسي، نائب رئيس غرفة التجارة في بيروت وجبل لبنان غابي تامر، رئيس مجلس إدارة شركة الصناعات الغذائية Difco Group عبدالله ضاهر، قائد منطقة البقاع الإقليمية في قوى الأمن الداخلي العميد نديم عبد المسيح، رئيس بلدية زحلة – المعلقة وتعنايل المهندس سليم غزالة، رئيس بلدية قاع الريم غسان صليبا، أساقفة المدينة، فعاليات سياسية اقتصادية واجتماعية وثقافية وإعلامية، وأصحاب الشركات المشاركة في المعرض.
+وبعد النشيد الوطني اللبناني، كانت كلمات لكل من عرّيفي الحفل رئيسة دائرة العلاقات العامة في غرفة التجارة والصناعة والزراعة في البقاع ماريا رزق الله، ومستشارة مركز غرفة الصناعة للتدريب المهندسة بوليت بو منصف، والأستاذ كمال بكري كلمات بالمناسبة.
+واستهل وزير الصناعة المهندس جو عيسى الخوري كلمته بتحية لأهالي زحلة والبقاع، معرباً عن "سعادته بالحفاوة والاستقبال"، مؤكداً أن "زيارة المنطقة تمنح الزائر شعوراً بأنه بين أهله وفي بيته".
+وتوجه عيسى الخوري بالشكر إلى "غرفة التجارة والصناعة والزراعة في زحلة والبقاع برئاسة منير التيني، وبلدية زحلة – المعلقة وتعنايل برئاسة المهندس سليم غزالة، وتجمع الصناعيين في البقاع برئاسة نقولا أبو فيصل، إضافة إلى جميع المؤسسات والأفراد الذين ساهموا في تنظيم هذا الحدث".
+واعتبر عيسى الخوري أن "اجتماع هذا العدد من العارضين في مكان واحد يتجاوز مفهوم المعرض التقليدي"، قائلاً إن "الحدث يحمل رسالة واضحة مفادها أن «البقاع يزرع، ويصنّع، ويصدّر، والأهم أنه يتمسّك بأرضه»".
+وأشار إلى "المكانة التي باتت تحتلها زحلة عالمياً، بعدما تم الاعتراف بها ضمن شبكة اليونسكو للمدن المبدعة في مجال فن الطهو"، لافتاً إلى أن "هذا الإنجاز هو ثمرة تاريخ طويل لمنطقة شكلت خزّاناً غذائياً أساسياً، وأناس عرفوا كيف يحولون خيرات أرضهم إلى منتجات وصناعات تحمل قيمة مضافة حقيقية".
+وأكد أن البقاع "يشهد اليوم تكاملاً متزايداً بين الزراعة والصناعة، من الكرمة التي تتحول إلى نبيذ وعرق يحصدان الجوائز، إلى الحليب ومشتقاته، والخضار والفاكهة والحبوب والقمح التي تدخل في صناعات المعلبات والزيوت والمقطرات وغيرها من المنتجات التي تحمل اسم لبنان إلى الأسواق المحلية والخارجية".
+وشدد عيسى الخوري على "أهمية الانتقال من تصدير المواد الخام إلى تصدير المنتجات المصنعة"، معتبراً أن "هذه الرؤية تشكل جوهر السياسة التي تسعى إليها وزارة الصناعة، لما لها من دور في خلق فرص العمل، وزيادة الصادرات، وإدخال العملة الصعبة، وتعزيز دور الزراعة كشريك أساسي في التنمية الصناعية".
+وتوقف الوزير عند "صمود أبناء المنطقة وتمسكهم بأرضهم رغم الأزمات والحروب والظروف الصعبة التي مر بها لبنان"، وقال "إن الخيار الأسهل كان الرحيل، إلا أن أبناء المنطقة اختاروا البقاء والإنتاج والاستثمار في أرضهم".
+وأضاف أن "الأرض بالنسبة إلى أبناء البقاع ليست مجرد ملكية، بل ذاكرة وهوية ومستقبل"، مشيداً "بقدرتهم على تحويل تعبهم إلى إنتاج، وإنتاجهم إلى مؤسسات، ومؤسساتهم إلى فرص عمل وكرامة لأبنائهم".
+وأكد أن "تمسك اللبناني بأرضه ليس عناداً، بل إيمان بأن «لا كرامة اقتصادية من دون إنتاج، ولا وطن من دون ناس متجذرين فيه»".
+ولفت عيسى الخوري إلى أن "المنتجات البقاعية استطاعت الوصول إلى الأسواق العالمية رغم كل الظروف والتحديات، معتبراً أن المنافسة بين المؤسسات الصناعية في المنطقة بحد ذاتها مؤشر إيجابي على وجود قطاع صناعي متكامل ينمو ويتطور".
+ودعا اللبنانيين إلى "زيارة البقاع والتعرف إلى منتجاته وإقامة الشراكات مع صناعييه، ووضع شعار «صُنع في البقاع» على رفوف منازلهم ومتاجرهم".
+وأكد أن "دعم الصناعة الوطنية لا يجب أن يبقى مجرد شعار، بل يجب أن يتحول إلى قرار يومي يتخذه المواطن عند اختيار المنتجات التي يشتريها، مردداً شعار: «اشتري لبناني… بيبقى القرار لبناني»".
+وختم وزير الصناعة بالتأكيد أن "البقاع يشكل جزءاً أساسياً من الرؤية الصناعية للوزارة، مشيراً إلى العمل على تسهيل عمل المؤسسات الصناعية، ودعم الجودة والتصدير، وتحسين البيئة الصناعية وتعزيز الشراكة بين الدولة والقطاع الخاص".
+وقال: «مبروك للبقاع، مبروك لزحلة، ومبروك لكل صناعي ومزارع وعامل يثبت كل يوم أن لبنان قادر على إنتاج الأفضل».
+وأضاف: «صُنع في البقاع… صُنع من كل لبنان».
+واختتم الوزير عيسى الخوري كلمته بأبيات شعرية مهداة إلى زحلة وأهلها:
+زحله يا أرض الكرَم والعزّ والخيرات
+انتي حكاية مجد، والتاريخ عنّك راوي
+بزورِك تا شوف الخير مزروع بالسهلات
+وترابِك شَمّتو عطر، وكِل جِرح بِداوي
+وعا أرض زحله جايي، حامل معي تحيّات
+لكلّ بقاعي أصيل، ولكلّ زحلاوي
+تحيّي للأرض اللي بدمّ ابطالا كتبتْ حكايات
+ولكلّ إيد بتنتج خير… وبتبني وَطن ضاوي
+الصّناعه يا زحله بسهلك عم ترفع الرايات
+والبيدر بفضل إيدين أهلك ما بقي خاوي
+دورو بالمعرض يا ضيوفنا وملّو هالساحات
+كل غرض هون بيقلّكن: أنا بقاعي وزحلاوي
+بدوره، شدد رئيس غرفة التجارة والصناعة والزراعة في زحلة والبقاع منير التيني على أن "معرض «صنع في البقاع» هو إحياء نابع من إيمان راسخ بأهمية الإنتاج في النهوض الاقتصادي واستعادة الصناعة لمكانتها في الاقتصاد الوطني".
+وأشار إلى أن "المعرض يُعتبر فرصة لعرض منتجات صناعيين ذوي خبرة طويلة، مؤكداً أن البقاع يمتلك المقومات التي تؤهله ليكون منطقة صناعية رائدة".
+وأوضح أن "الرؤية الحالية تتركز على تعزيز التجارة والصناعة والزراعة، مع اعتبار البقاع بوابة لبنان إلى العالم العربي ومنصة اقتصادية ولوجستية".
+واقترح التيني ثلاثة محاور رئيسية لتعزيز الاقتصاد، هي المعابر الجغرافية، والمعابر الجوية، والسكك الحديدية، بهدف تحسين الربط التجاري.
+وأضاف أن "هناك خطة لإنشاء منطقة اقتصادية حرة تربط هذه المحاور وتوفر فرص عمل للبنانيين"، مشيراً إلى أن "هذه الرؤية تتطلب استراتيجية وطنية للصناعة يتم وضعها بالتعاون مع الجهات المعنية".
+كما أعلن أن "غرفة زحلة تعمل على إنشاء مركز للتكنولوجيا والذكاء الاصطناعي لتدريب الشباب ودعم المؤسسات الاقتصادية".
+واعتبر أن "العودة إلى «صنع في البقاع» بعد تسع سنوات تُمثل بداية جديدة للاعتماد على الإنتاج بدلاً من الاستهلاك، وتحويل التركيز من تصدير الأفراد إلى تصدير المنتجات والأفكار".
+من جهته، أشاد رئيس تجمع الصناعيين في البقاع نقولا أبو فيصل بجهود غرفة التجارة ورئيس البلدية في دعم الصناعة المحلية وتنظيم هذا المعرض.
+وتقدم أبو فيصل "باقتراح مشروع لتحويل فائض إنتاج العنب إلى دبس، مؤكداً أهمية التعاون بين القطاعين العام والخاص لتعزيز النمو الاقتصادي في المنطقة، مع التركيز على الصناعة والزراعة كمقومات أساسية للصمود".
+كما تم التطرق إلى "الحاجة لتسهيل المعاملات الإدارية وزيادة عدد الملحقين التجاريين في السفارات، بهدف تعزيز الصادرات اللبنانية".
+وأكد أبو فيصل "أهمية الصناعات الغذائية في زحلة ودورها في الاقتصاد اللبناني، داعياً إلى تقليل التبعية للاقتصاد الريعي وتعزيز الإنتاج المحلي".
+وأعرب عن "قلقه من التشهير بالصناعة اللبنانية، مؤكداً اتخاذ إجراءات قانونية ضد أي تعدٍّ".
+واختتم كلمته "بالشكر للمنظمين، والتأكيد على أهمية الاستمرار في دعم الصناعة المحلية لتحقيق النمو الاقتصادي المستدام".
+من جانبه، أكد رئيس بلدية زحلة – المعلقة وتعنايل المهندس سليم غزالة أن "البقاع أثبت رغم كل التحديات والظروف الصعبة، قدرته على الإنتاج والإبداع وصناعة الفرص"، مشيداً "بالدور المحوري الذي يشكّله القطاع الصناعي في المنطقة كجزء أساسي من مسيرة النهوض الاقتصادي اللبناني".
+وشدّد على "ضرورة الانتقال إلى رؤية أكثر تكاملاً، تقوم على إنشاء منطقة اقتصادية وصناعية متطورة تجمع بين الصناعة والزراعة والتكنولوجيا والخدمات اللوجستية، بما يعزز موقع البقاع كمركز إنتاجي واقتصادي فاعل".
+كما دعا إلى "تطوير مركز للتكنولوجيا والابتكار يحتضن الشركات الناشئة ويساهم في تطوير المهارات، لا سيما في مجالات الذكاء الاصطناعي والتقنيات الحديثة، بالتوازي مع تعزيز الربط بشبكة لوجستية عصرية تواكب متطلبات الاقتصاد الحديث".
+وفي هذا السياق، اعتبر أن "مطار رياق يشكّل عنصراً محورياً ضمن مشروع اقتصادي وطني متكامل، لما يمكن أن يوفره من فرص في مجال الشحن الجوي والخدمات اللوجستية وربط المنطقة بالأسواق المحلية والإقليمية والدولية".
+وأكد أن "تحقيق هذه الرؤية يتطلب شراكة حقيقية بين الحكومة والبلديات والقطاع الخاص، بهدف تحويل البقاع إلى مركز صناعي وغذائي متقدم ومنصة لوجستية إقليمية".
+وختم بالتأكيد أن "معرض «صنع في البقاع» يشكّل دليلاً حياً على وجود الطاقات والكفاءات وروح المبادرة"، داعياً إلى "البناء على هذه النجاحات وتعزيزها، لتحويل قصص النجاح الفردية إلى مشروع اقتصادي متكامل يساهم في تحقيق التنمية المستدامة والنهوض بالاقتصاد اللبناني".
+وفي ختام حفل الافتتاح، كرّمت غرفة زحلة بدروع تكريمية، كل من وزير الصناعة المهندس جو عيسى الخوري تقديراً لجهوده في تعزيز الصناعة ودعمه الصناعيين، ورئيس تجمع الصناعيين في البقاع نقولا أبو فيصل، والسيد عبدالله ضاهر كأفضل صناعي عن عام 2025، ورئيس بلدية زحلة – المعلقة وتعنايل المهندس سليم غزالة، ومدير برنامج الطاقة والقطاع الخاص في منظمة ICU ماريو غريّب.
+بعدها، جال الوزير عيسى الخوري يرافقه رئيس الغرفة والوزراء الحاضرون على أجنحة الصناعيين المشاركين في المعرض، حيث اطلعوا على منتجاتهم وتعرفوا إلى مختلف الصناعات البقاعية المشاركة.</t>
+        </is>
+      </c>
+      <c r="E129" t="inlineStr">
+        <is>
+          <t>2026-10-29T11:21:39.719432+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" t="inlineStr">
+        <is>
+          <t>عيسى الخوري يحقّق مع معهد البحوث الصناعية لادخاله شحنة اسمنت من دون فحوصات وطلب اتّخاذ الاجراءات الق</t>
+        </is>
+      </c>
+      <c r="B130" t="inlineStr">
+        <is>
+          <t>http://www.industry.gov.lb/Media/News/عيسى-الخوري-يحقق-مع-معهد-البحوث-الصناعية-لادخا-(1)</t>
+        </is>
+      </c>
+      <c r="C130" t="inlineStr">
+        <is>
+          <t>2011-01-01</t>
+        </is>
+      </c>
+      <c r="D130" t="inlineStr">
+        <is>
+          <t>عيسى الخوري يحقّق مع معهد البحوث الصناعية لادخاله شحنة اسمنت من دون فحوصات وطلب اتّخاذ الاجراءات القانونيّة بحقّ المتقاعسين
+وجّه وزير الصناعة جو عيسى الخوري كتاباً إلى مدير عام معهد البحوث الصناعية "طلب فيه إجراء تحقيق فوري مع الموظفين المعنيّين بإدخال شحنة إسمنت عبر مرفأ طرابلس لصالح شركة دير عمار ميتال ش.م.م دون إخضاعها للفحوصات اللازمة لدى معهد البحوث الصناعية، وإتخاذ الإجراءات المناسبة بحقّهم."
+وإذ شدّد عيسى الخوري على "إيداعه كافة المستندات المتعلّقة بالملف ونتيجة التحقيق بالسرعة القصوى."
+وأضاف في كتابه:" لقد تبيّن أن الشحنة المذكورة تم إدخالها بناء على إفادة صادرة عن معهد البحوث الصناعية وموجّهة لإدارة الجمارك اللبنانية تفيد بأن "البضاعة غير خاضعة لأحكام المراسيم الإلزامية المكلف بتطبيقها و/أو لكونها بكميات إفرادية قليلة". علماً أنّه لا يمكن إدخال الإسمنت المستورد إلى السوق اللبناني إلا بعد الحصول على إفادة صادرة من معهد البحوث الصناعية بالموافقة، وذلك بموجب المرسوم رقم ٩٧٦٦ تاريخ ۲۰۰۳/۳/۱۱ (إعطاء صفة الإلزام للمواصفة القياسية اللبنانية رقم ٥٣ المتعلقة بالإسمنت). وكان مدير عام وزارة الصناعة أبلغ المديرية العامة للجمارك بموجب كتابه رقم ٢٠١٦/١٣٤٩ - ۲۱٥ ص تاريخ ۲۰۲٦/٧/١٥ بذلك. ولما كان عمل معهد البحوث الصناعية يتعارض مع المراسيم المرعية ويخالف تعليمات وزارة الصناعة ويمكن أن يتسبّب بمخاطر كبيرة خاصة لجهة السلامة العامة في الأبنية والإنشاءات في حال عدم مطابقة الشحنة للمواصفات، طلب الوزير عيسى الخوري من معهد البحوث الصناعية سحب الإفادة المذكورة وإبلاغ المديرية العامة للجمارك بقرار السحب وعدم العمل بها".</t>
+        </is>
+      </c>
+      <c r="E130" t="inlineStr">
+        <is>
+          <t>2026-10-29T11:21:42.331275+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" t="inlineStr">
+        <is>
+          <t>الهيئات الإقتصادية تستضيف وفداً إقتصادياً إماراتياً رفيع المستوى برئاسة وزير التجارة الخالجية ويضم ن</t>
+        </is>
+      </c>
+      <c r="B131" t="inlineStr">
+        <is>
+          <t>http://www.industry.gov.lb/Media/News/الهييات-الاقتصادية-تستضيف-وفدا-اقتصاديا-اماراتيا-ر</t>
+        </is>
+      </c>
+      <c r="C131" t="inlineStr">
+        <is>
+          <t>2011-01-01</t>
+        </is>
+      </c>
+      <c r="D131" t="inlineStr">
+        <is>
+          <t>الهيئات الإقتصادية تستضيف وفداً إقتصادياً إماراتياً رفيع المستوى برئاسة وزير التجارة الخالجية ويضم نحو 90 رجال أعمال إنعاقد ملتقى إقتصادي لبناني إماراتي ولقاءات وزارية وإجتماع عمل لإتحادي الغرف ومجلس الأعمال المشترك: تأكيد على تطوير التعاون الإقتصادي وترسيخ الشراكة الإستثمارية في مختلف المجالات
+إستضافت الهيئات الإقتصادية وإتحاد الغرف اللبنانية برئاسة الوزير السابق محمد شقير، وفدداً إماراتياً رفيع المستوى برئاسة وزير التجارة الخارجية في الإمارات ثاني بن أحمد الزيّودي، وضم ما يناهز 90 شخصية من كبار رجاال الأعمال والمستثمرين والقيادات الإقتصادية الإماراتية.
+وذلك بهدف تعزيز التعاون بين القطاع الخاص في البلدين وإستكشاف الفرص وترسيخ الشراكة الإقتصادية والإستثمارية بشكل مستدام بين البلدين.
+إجتماع إتحاد الغرف في البلدين
+وإنطلقت فعاليات الزيارة بعقد اجتماع بين اتحاد الغرف اللبنانية برئاسة الوزير السابق محمد شقير واتحاد الغرف الإماراتية برئاسة نائب رئيس اتحاد غرف الإمارات سلطان عبدالله العويس في Seaside Arena ، تم خلاله البحث في توطيد العلاقات ومتطلبات تسهيل الأعمال وزيادة حجم التجارة البينية وتقوية الشراكات وترسيخ التعاون في لبنان وسوريا والعراق ودول المنطقة.
+وتم الاتفاق على زيادة التواصل والتنسيق وتبادل الزيارات لتحقيق الأهداف المرجوة، وللاستفادة من التجارب وتبادل الخبرات.
+لقاءات عمل ثنائية
+وبالتزامن عقد لقاءات عمل ثنائية (B2B) بين 50 رجل أعمال من الوفد الإماراتي وحوالي 120 رجل أعمال من الجانب اللبناني في مختلف القطاعات تجارة، صناعة، زراعة، سياحة، تكنولوجيا معلومات، بترول، غاز ومصارف والبنى التحتية وخدمات، وذلك بهدف استكشاف الفرص والبحث في إمكانية إقامة شراكات عمل بين الشركات اللبنانية والشركات الإماراتية .
+لقاءات الوزير الزيودي
+وبعد وصوله الى Seaside Arena أجرى الوزير الزيّودي لقاءات متتالية مع رئيس الهيئات الاقتصادية الوزير السابق محمد شقير ووزير الاقتصاد والتجارة عامر البساط ومن ثم مع وزير الصناعة جو عيسى الخوري، ووزير الأشغال العامة والنقل فايز رسامني، ووزير الدولة لشؤون تكنولوجيا المعلومات الدكتور كمال شحادة، رسامني حيث جرى بحث سبل تعزيز التعاون والفرص المتاحة والشراكات التي يمكن عقدها بين الجانبين من أجل تحقيق قفزة نوعية في العلاقات الاقتصادية الثنائية وترسيخ الشراكة المستدامة.
+لقاءات عمل مستدامة
+وبدأت فعاليات الملتقى عند الساعة 3:00 وبدأ الإفتتاح بالنشيدين الوطنيين ثم كلمة لعريف الإحتفال الإعلامي موريس متى.
+شقير
+في البداية ألقى رئيس الهيئات الاقتصادية الوزير السابق محمد شقير كلمة جاء فيها: يسعدني ويشرّفني، باسم جميع اللبنانيين أن أرحّب أشدّ الترحيب بالوفد الاقتصادي الإماراتي الشقيق، برئاسة معالي الوزير الدكتور ثاني بن أحمد الزيودي، وأن أعرب أمامكم عن بالغ سروري وسعادتي بوجوده في لبنان. فنحن في لبنان وفي بيروت تحديداً، اشتقنا للقاء أشقائنا الإماراتيين، الذين نعتبرهم أخوة أعزاء تجمعنا بهم روابط عميقة ومتجذّرة من المحبة والأخوة والاحترام.
+وعبر شقير عن تفائله باستقبال الوفد اليوم كونه أول وفد اقتصادي بهذا الثقل يأتي إلى لبنان بعد سنوات صعبة مررنا خلالها بالانهيار المالي، وجائحة كورونا، والحرب التي اندلعت في 7 أكتوبر، مشدداً إن وجودكم بيننا بشرى خير، ورسالة أمل، ودليل على أن بلدنا بدأ يتعافى ويستعيد مكانته. وتأكيد أيضاً بأن لبنان مع فخامة رئيس الجمهورية العماد جوزاف عون، ودولة رئيس مجلس الوزراء الدكتور نواف سلام، ودولة رئيس مجلس النواب نبيه بري، بدأ يستعيد تدريجيًا ثقة الدول العربية الشقيقة والمجتمع الدولي.
+ولفت شقير لا شك أن لقاء القمة بين فخامة الرئيس جوزاف عون وصاحب السمو الشيخ محمد بن زايد آل نهيان، رئيس دولة الإمارات، أسس لهذا المسار الجديد، وأسفر عن خطوات مهمة، أبرزها: إنشاء مجالس الأعمال بين البلدين، ورفع حظر سفر الأشقاء الإماراتيين إلى لبنان، وصولًا إلى زيارة هذا الوفد الاقتصادي الرفيع اليوم.
+واعتبر أن هذه خطوات متتالية تعكس إرادة واضحة لإعادة فتح صفحة جديدة من التعاون والاستثمار والشراكة. ونحن كقطاع خاص لبناني، نرى أن هناك إمكانية متاحة لتفعيل التعاون الاقتصادي بين البلدين على نحو أوسع وأعمق، وهذا أمر طبيعي كوننا نبني على نجاح كبير حققته الشراكة بين رجال الأعمال اللبنانيين وأشقائهم الإماراتيين في الإمارات، وعلى قوة علاقاتنا الأخوية، وعلى المزايا التفاضلية التي نمتلكها، وعلى الطاقات والخبرات والكفاءات الكبيرة التي يتمتع بهما القطاع الخاص في لبنان والإمارات.
+وأكد أنه لدينا الكثير من الطاقات والفرص الواعدة التي يمكن أن نبني فيها شراكات ناجحة ومستدامة. وقد لمسنا ذلك بوضوح منذ الفعالية الأولى لهذا الملتقى، والمتمثلة في لقاءات العمل الثنائية، التي جمعت نحو 50 شخصية اقتصادية إماراتية مرموقة مع عدد كبير من رجال الأعمال الللبنانيين، وفي مختلف القطاعات.
+ولفت إلى أن هذه اللقاءات الثنائية هي ربما الأكثر تعبيرًا عن جوهر ما نريد أن نبنيه معًا؛ لأن العلاقات الاقتصادية الحقيقية لا تُبنى فقط بالاتفاقيات، بل تُبنى بالشراكات، وبالمشاريع، وبالاستثمارات، وبخلق فرص العمل والقيمة المضافة في البلدين.
+وأضاف فإن لبنان مقبل بإذن الله على مرحلة واعدة، سيبدأ معها عملية إعادة الإعمار وتطوير بناه التحتية ومرافقه الإقتصادية والخدماتية، وفي هذا الجانب لدينا مشاريع كثيرة التي يمكن الدخول فيها عبر الشراكة بين القطاعين العام والخاص والتلزيم عبر الـBOT، وقد بدأت بشائر هذا التوجه الحكومي تظهر بوضوح من خلال تلزيم إحدى الشركات بإعادة تطوير وتشغيل مطار الرئيس رينه معوض في القليعات في عكار.
+حقيقةً، نحن أمام فرص كبيرة، وطموحنا لا يجب أن يتوقف عند حدود بلدينا. فالتكامل بين الخبرات والقدرات اللبنانية والإماراتية يمكن أن يفتح آفاقًا أوسع للتعاون في أسواق شقيقة واعدة، لا سيما في سوريا والعراق، وصولًا إلى الأسواق الإفريقية وغيرها.
+وتابع شقير قائلاً نحن على ثقة بأن ما يجمع لبنان والإمارات أكبر بكثير من المصالح الاقتصادية؛ إنه تاريخ من الأخوة والثقة والتعاون، ولا بد من ترجمته إلى شراكة اقتصادية جديدة، أكثر قوة واتساعًا واستدامة.ختاماً، نسأل الله أن يحمي الإمارات ولبنان وشعبيهما، وأن ينهي دوامة الحروب، ويمن على منطقتنا ودولنا بالأمن والإستقرار والسلام.
+العويس
+ثم ألقى نائب رئيس اتحاد غرف الإمارات سلطان عبدالله العويس كلمة جاء فيها: إن هذا اللقاء الاقتصادي من شأنه أن يفتح الطريق أمام إعادة تنشيط وزيادة حجم التبادل التجاري بين دولة الإمارات العربية المتحدة والجمهورية اللبنانية. فالعلاقات الاقتصادية بين الإمارات ولبنان تعود إلى عقود طويلة، وقد شهدت منذ سبعينيات القرن الماضي تطوراً متسارعاً في بناء الشراكات الاقتصادية وتعزيز حركة التبادل التجاري بين البلدين.
+وأضاف نحن في اتحاد غرف التجارة والصناعة، نعمل بالتعاون مع زملائنا في لبنان على تعزيز هذه العلاقات، وقد عقدنا صباح اليوم لقاءات تهدف إلى تبادل الخبرات بين غرف الإمارات واتحاد الغرف في الجمهورية اللبنانية، انطلاقاً من هدف أساسي يتمثل في تقوية وزيادة حجم التبادل التجاري والاستثماري، وتعزيز تبادل الخبرات بين دولة الإمارات العربية المتحدة والجمهورية اللبنانية.
+كما أن الكلمات الإيجابية والمحفزة للاستثمار في الجمهورية اللبنانية تشكّل دافعاً مهماً أمام القطاع الخاص الإماراتي لزيادة استثماراته في مختلف القطاعات، لا سيما الصناعة، والخدمات اللوجستية، والفنادق، والقطاع الصحي، وغيرها من القطاعات التي من شأنها أن تسهم في تعزيز العلاقات الاقتصادية والتجارية بين البلدين.
+وفي هذا الإطار، نتقدم بجزيل الشكر والتقدير إلى سفير دولة الإمارات العربية المتحدة لدى الجمهورية اللبنانية، وسفير الجمهورية اللبنانية لدى دولة الإمارات العربية المتحدة، لما يقومان به من دور مهم في تعزيز العلاقات بين البلدين وإنجاح هذا اللقاء.
+شحادة
+أما شحادة فاعتبر أن لبنان اليوم على سكةِ التعافي، ويتقدّم بثباتٍ على ثلاثةَ محاورَ أساسية: بسط سلطةٍ الدولةِ على كاملٍ أراضيها، والمضيّ في مسار الإصلاحِ المالي والاقتصادي، وتثبيت سيادة القانون. وهذه المسارات هي الأساس لخلق بيئةٍ مستقرةٍ وجاذبة للاستثمار، ولتحويلِ الفرصِ التي نناقشُها اليومَ إلى مشاريعَ وشراكاتٍ مستدامة. وفي هذا السياق، لا بدّ من أن نوجّهَ الشكرَ إلى دولةِ الإمارات العربية المتحدة على دعمِها المستمرِ للبنانَ خلالَ السنواتِ الماضية، وعلى وقوفِها إلى جانبِ الشعبِ اللبناني. ونقدّرُ اليوم بشكلٍ خاص استضافتَها الكريمةَ للجاليةِ اللبنانيةِ. وهذه العلاقة الإنسانية والاقتصادية العميقة تشكّل رصيدًا مهمًا نبني عليه شراكتَنا المستقبلية.
+وأكد إنّ وجودَكم اليومَ في لبنانَ يشكّل للإمارات فرصةً لفتحِ صفحةٍ جديدةٍ في الشراكةِ بين لبنانَ ودولةِ الإماراتِ، شراكةً نريدُ لها أن تقومَ على الاستثمارِ، والتكنولوجيا، والابتكارٍ، وبناءِ اقتصادٍ رقميّ مشتركٍ.
+وأضاف لقد رسّختْ دولةُ الإماراتِ موقعَها كقوةٍ عالميةٍ في التكنولوجيا والذكاءِ الاصطناعيّ والاقتصادِ الرقميّ، لا كرائدةٍ في منطقتِنا فحسبْ بل عالمياً.كما أدخلتِ دولة الإمارات التكنولوجيا وممارساتِ القطاعِ الخاصِّ إلى صميم عملِها:حكومةٌ بلا ورقٍ، وخدماتٌ رقميةٌ متكاملةٌ، وإدارة قائمةٌ على مؤشراتِ الأداءِ والقياسِ المستمرِّ، حتى غدا الأداءُ الحكوميُّ الإماراتيُّ نفسُه معيارًا عالميًا.
+أما لبنانُ، فيمتلك طاقاتٍ بشريةً استثنائيةً، من مهندسينَ ومطوّرينَ وروّادِ أعمالٍ وباحثينَ ومبتكرينَ، إضافةً إلى جامعاتٍ عريقةٍ وقطاعِ خاصٍّ يتمتعُ بقدرةٍ كبيرةٍ على الابتكارِ والتوسَّع خارجَ الحدود.
+ما نريدُه هو شراكةٌ ندّيةٌ لمصلحة الطرفين، ويبني فيها كلُّ طرفٍ على نقاطِ قوةِ الآخر .
+ومن هنا، فإنّ طموحَنا يتجاوزُ مجردَ مجموعةٍ من المشاريع.
+نريدُ أن نفتحَ أمامَ الشركاتِ والمواهبِ اللبنانيةِ أسواقًا جديدةً، وفي الوقتِ نفسه أن نخلقَ أمامَ الشركاتِ والاستثماراتِ الإماراتيةِ فرصا جديدةً في لبنانَ والمنطقةِ.
+لكنْ طموحُنا أكبرُ من ذلكَ، طموحنا أن نجمعَ قدراتنا لكي ننجز معاً ما يصعبُ على أيّ منا أنجازَه منفرداً.
+وإذا جمعنا مقوّماتِ البلدين، يمكنُنا أن نبنيَ معًا شركاتٍ ومنتجاتٍ وخدماتٍ قادرةً ليس فقط على المنافسةِ في أسواقِنا، بل على المنافسةِ في الأسواقِ العالميةِ.
+كما أن طموحَنا أن نعملَ تدريجيًا باتجاهِ سوقٍ رقميةٍ مشتركةٍ بين لبنانَ والإماراتِ، تحكمُها قواعدُ ومعاييرُ متناسقةٌ، بحيثُ يصبحُ عملُ الشركاتِ والاستثماراتِ والخدماتِ الرقميةِ والبياناتِ والمواهب بين بلدَينا أسهلَ وأكثرَ كفاءةً.
+ونتطلَعُ، أبعدَ من ذلكَ، إلى بناءِ شراكةٍ تشكّلُ نموذجًا يُحتذى به إقليميًا، وتفتحُ الطريقَ أمامَ إنشاءِ سوقٍ موحدةٍ
+عيسى الخوري
+أما الوزير عيسى الخوري فاعتبر أن العلاقة بين لبنان ودولة الإمارات العربية المتحدة لم تكن يوماً إلّا علاقة أخوّةٍ وصداقة بين الاماراتيين واللبنانيين. إنها علاقة تاريخيّة ومتينة٫ نسجها أناسٌ مِقدامون قبل أن تنصَّ عليها الاتفاقيات. فمنذ السنوات الأولى لقيامِ الاتحاد، كان مصرفيّون ومهندسون وأساتذة وأطباء وصناعيّون وتجّار لبنانيّون، في طليعة مَنْ قصدَ الامارات ليساهموا في بنائها، ووضعوا علومَهم وخبراتِهم وكفاءاتهم، وشبكوا أيديهم مع أبناء البلد، في سبيل قيام دولة عصرية ومتطوّرة. في المقابل، فتحتِ الإمارات أبوابها أمامَهم من دونِ تحفّظ، في أيام ازدهار لبنان، والأهمُ من ذلك، في أحلك أيّامه وأصعبها. ولبنان لا ينسى ذلك. ونحن لا ننسى من وقف إلى جانبنا.
+لكن دعوني أتحدثُ عمّا تغيّر. فعلى مدى عقودٍ، تمحورتِ العلاقة حول مساهمةِ الكفاءات اللبنانيةِ في مسيرةِ نهوضِ الإمارات. أما اليوم، فقد دخلت فصلا جديداً رائعاً: إذ أصبحت دولة الإمارات منصّةً رائدةً ومتقدّمة، ليس في مِنطقتنا فحسب، بل على مستوى العالم. منصّةٌ للمال والأعمال، والخدمات اللوجستية، والتكنولوجيا، والاستثمار، والأفكار.
+وقال الآن، سأتحدث بوضوح، بصفتي وزيراً للصناعة يخاطب رجالَ وسيدات الأعمال، فأهلُ الأعمال يُقدرون الكلامَ الصريح. أنتم تسمعون، في العديد من المحافل، حديثاً عن حاجة لبنان إلى المنح والمساعدات والدعم. هذا الحديثُ يتعلقُ بالقطاعِ العام، وهو حديثٌ مشروع.
+لكنه ليس حديثُ القطاع الخاص اللبناني. فالقطاع الخاص الماثلُ أمامَكم اليوم لا يطلبُ مِنحاً، ولا يطلبُ مساعدات. القطاعُ الخاص يقترحُ أمراً واحداً: استثمارَكم في لبنان وشراكتَنا معكم، استثمارٌ بشروطٍ تجارية، يُقَيّم وِفق جدواهُ التجارية، ويُحقِقُ عوائدَ تجارية. لقد صمد الصناعيون اللبنانيون في وجهِ كلّ أزمةٍ مرٌ بها هذا البلد. وبقوا مستمرّين، ينتجون ويصدٌرون وينافسون.
+واعتبر عيسى الخوري إنهم ليسوا عبئاً يحتاجُ إلى الدعم. إنهم فرصةٌ تستحقُ الاستثمار.وهذه الفرصة أوسعَ مما قد تتوقعون.
+البساط
+والقى البساط كلمة ركّزَ فيها على أربعِ نقاطٍ أساسيّة. أولاً: قدراتُ لبنانَ الإنتاجيّةُ أكبرُ بكثيرٍ ممّا يُنتجُه اليوم، لدينا قطاعٌ خاصٌّ ديناميكيّ، وكفاءاتٌ بشريّةٌ استثنائيّة، وعلاقاتٌ عميقةٌ مع المنطقةِ والعالم. هذه المقوّماتُ لم تختفِ بسببِ الأزمة. ويمكنُ لهذه الإمكاناتِ أن تتحوّلَ إلى فرصٍ حقيقيّة. فالفرصُ الاستثماريّةُ الكبرى تبدأُ أحياناً قبلَ اكتمالِ التعافي، عندما تبدأُ ملامحُه بالظهور. ومن هنا تأتي أهميّةُ زيارتِكم اليوم. ثانياً: الإمكاناتُ وحدَها لا تكفي، فإن تحويلُها إلى نموٍّ وازدهارٍ يحتاجُ إلى إصلاحٍ حقيقيّ: للقطاعِ المصرفيّ، وللإطارِ الماليّ، وللخدماتِ الأساسيّة، ولطريقةِ عملِ الدولة. ويحتاجُ أيضاً إلى ترسيخِ مبدأٍ غيرِ قابلٍ للتفاوض: سيادةِ الدولة، وحصريّةِ السلاح، وقرارِ الحربِ والسِّلمِ بيدِ الدولةِ وحدَها، مؤكداً أن لا اقتصادَ يزدهر، ولا مستثمرَ يخطّطُ بثقة، إذا لم تكنْ هذه القراراتُ بيدِ الدولةِ وحدَها. ثالثاً: التعافي يجبُ أن يكونَ، في جوهرِه، مشروعَ القطاعِ الخاص.وهنا تقدّمُ الإماراتُ نموذجاً مهمّاً: دولةٌ لا تحلُّ مكانَ القطاعِ الخاص، بل تهيّئُ له شروطَ النجاح — وضوحُ القواعد، وسهولةُ ممارسةِ الأعمال، والتخطيطُ بعيدُ المدى، والانفتاحُ على الكفاءاتِ ورؤوسِ الأموالِ والأسواقِ العالميّة. ولدينا أساسٌ قويٌّ للبناء عليه. فالقطاعُ الخاصُّ اللبنانيُّ من أكثرِ القطاعاتِ ريادةً في المنطقة، وجزءٌ كبيرٌ منه وجدَ في الإماراتِ بيتاً ثانياً.لذلك، حين أنظرُ إلى هذه القاعة، لا أرى وفدَيْن اقتصاديَّيْن غريبَيْن عن بعضِهما، بل مجتمعَ أعمالٍ تربطُه علاقاتٌ وشراكاتٌ بُنِيَتْ على مدى عقود. رابعاً: علينا أن نحوّلَ هذه العلاقةَ إلى شراكةٍ اقتصاديّةٍ أعمق. ومن أهمِّ عناصرِ التجربةِ الإماراتيّةِ اندماجُها في الاقتصادِ العالميّ. كان ذلك خياراً واعياً، تُرجِمَ باتفاقيّاتِ التجارةِ والشراكاتِ الاقتصاديّةِ الشاملة. لبنانُ تأخّرَ كثيراً في هذا المجال. وحانَ الوقتُ لكي نغيّرَ ذلك.
+لذلك، أطرحُ اليومَ أن نبدأَ باستكشافِ إطارِ شراكةٍ اقتصاديّةٍ خاصّةٍ بين لبنانَ والإمارات — مساراً عمليّاً لتعميقِ التجارةِ والاستثمار، ونقلِ المعرفة، وربطِ شركاتِنا وأسواقِنا. ونريدُ، في ذلك، ليس فقط شراكتَكم، بل أيضاً الاستفادةَ من تجربتِكم وخبرتِكم.
+الزيودي
+أما الوزير الزيودي فقال يسعدني أن أكون بينكم اليوم في مستهل أعمال منتدى الأعمال الإماراتي اللبناني الذي يجمع نخبة من قادة الأعمال والمستثمرين وصناع القرار من دولة الإمارات العربية المتحدة والجمهورية اللبنانية الشقيقة. وفي البداية، أتوجه بخالص الشكر والتقدير إلى الأشقاء اللبنانيين، على ما حظينا به من حفاوة استقبال وكرم ضيافة، كما أشكر القائمين على تنظيم هذا المنتدى الذي يجسد حُسن تنظيمه روح الفريق الواحد التي تجمع بلدينا الشقيقين.
+واعتبر أن العالم يشهد حالياً تحولات متسارعة في أنماط التجارة والاستثمار وسلاسل الإمداد والاقتصاد الرقمي والتكنولوجيا المتقدمة. وفي ظل هذه المتغيرات، أصبحت الشراكات الاقتصادية الفاعلة أكثر أهمية من أي وقت مضى، ليس فقط لتحقيق النمو، وإنما لتعزيز القدرة على المنافسة والاستفادة من الفرص التي تتيحها الأسواق العالمية سريعة التغير. ومن هذا المنطلق، تأتي أهمية هذا المنتدى الذي يجمعنا اليوم. فهو ليس مجرد منصة للحوار وتبادل الأفكار، بل مساحة عملية لاستكشاف فرص جديدة للتعاون، وبناء شراكات نوعية، وتطوير مشاريع قادرة على تحقيق قيمة مضافة حقيقية لاقتصادَي بلدينا الشقيقين.
+فلقد أثبتت التجارب الناجحة حول العالم أن الحكومات تستطيع أن ترسم الرؤى وتوفر بيئة الأعمال المٌمكنة للنجاح، لكن القطاع الخاص يبقى المحرك الرئيسي للنمو الاقتصادي والابتكار وخلق الوظائف واستقطاب الاستثمارات. ومن هنا، فإن نجاح العلاقات الاقتصادية بين الدول يقاس في نهاية المطاف بعدد الشراكات التي تُبنى، والاستثمارات التي تُنفذ، والفرص التي تُخلق على أرض الواقع.
+ولذلك فإننا ننظر إلى الإخوة والأخوات المشاركين في هذا المنتدى من قادة الأعمال وممثلي القطاع الخاص بوصفهم شركاء أساسيين في صياغة المرحلة المقبلة من التعاون الاقتصادي البناء بين الإمارات ولبنان.
+لدينا اليوم أسس قوية للبناء عليها والانطلاق إلى آفاق أرحب من التعاون التجاري والاستثماري الذي يحقق التطلعات التنموية لبلدينا وشعبينا الشقيقين. فقد بلغت قيمة تجارتنا غير النفطية 4.2 مليار دولار أمريكي خلال عام 2025، محققة نمواً سنوياً بنسبة 35.6%. وهذه الأرقام تعكس الإمكانات الكبيرة المتاحة أمامنا لمواصلة توطيد شراكتنا الاقتصادية خلال السنوات المقبلة.
+كما أن المشاركة الواسعة للقطاع الخاص ومجتمع الأعمال الإماراتي في هذه الزيارة تعكس مستوى الثقة المتزايد بالفرص المتاحة في السوق اللبنانية، والرغبة الجادة في بناء شراكات طويلة الأمد تقوم على تحقيق المصالح المتبادلة والنمو المشترك.
+فالوفد الإماراتي المشارك معنا اليوم يضم ممثلين عن مجموعة واسعة من القطاعات الحيوية، تشمل الخدمات اللوجستية، والأمن الغذائي، والزراعة، والرعاية الصحية، والنفط والغاز، والطاقة المتجددة، والطيران، والذكاء الاصطناعي، والسياحة. وهذه القطاعات لا تمثل فقط مجالات للتعاون، بل تشكل محركات رئيسية للنمو الاقتصادي والتنمية المستدامة في المستقبل.
+ونؤمن بأن هناك فرصاً واعدة للتعاون في هذه القطاعات الواعدة، بما يسهم في تعزيز تنافسية اقتصادَي البلدين وإيجاد فرص جديدة للقطاع الخاص.
+كما نؤمن بأن لبنان يمتلك ثروة حقيقية تتمثل في موارده البشرية وكفاءاته العلمية. وقد أثبتت الجالية اللبنانية حضوراً متميزاً في دولة الإمارات، وأسهمت عبر عقود في العديد من قصص النجاح في قطاعات الأعمال والابتكار والتكنولوجيا والخدمات المهنية.
+لقد تبنت دولة الإمارات خلال السنوات الماضية رؤية واضحة تقوم على بناء شراكات اقتصادية عالمية طويلة الأمد، وتعزيز انفتاحها على الأسواق الواعدة، وترسيخ مكانتها كمركز عالمي للتجارة والاستثمار.
+وفي هذا الإطار، أطلقت الدولة برنامج اتفاقيات الشراكة الاقتصادية الشاملة، الذي نجح في بناء شبكة متنامية من الشراكات التجارية والاستثمارية مع عدد من أسرع الاقتصادات نمواً في العالم، بما يسهم في تسهيل تدفقات التجارة والاستثمار، ويفتح آفاقاً جديدة أمام القطاع الخاص للوصول إلى أسواق عالمية استراتيجية.
+ومن هنا، أود أن أوجه الدعوة إلى مجتمع الأعمال اللبناني للاستفادة من هذه المنظومة المتكاملة، ومن شبكة الشركاء التجاريين والاستثماريين لدولة الإمارات الممتدة عبر مختلف القارات. فالإمارات حالياً لا توفر فقط بيئة أعمال تنافسية وموقعاً استراتيجياً وبنية تحتية عالمية المستوى، بل توفر أيضاً بوابة للوصول إلى أسواق تضم مليارات المستهلكين حول العالم.
+ونرى أن الشركات اللبنانية، بما تمتلكه من خبرات وكفاءات وقدرات تنافسية، مؤهلة للاستفادة من هذه الفرص، سواء من خلال التوسع انطلاقاً من دولة الإمارات نحو الأسواق العالمية، أو عبر بناء شراكات استراتيجية مع الشركات الإماراتية والدولية العاملة في الدولة.
+إننا ننظر إلى المرحلة المقبلة بتفاؤل وثقة. واليوم، تتهيأ أمامنا فرصة حقيقية للانتقال بعلاقاتنا الاقتصادية إلى مستوى جديد، فأفضل الشراكات هي تلك التي تُبنى على الثقة، وأفضل الاستثمارات هي تلك التي تخلق أثراً مستداماً، وأفضل الفرص هي تلك التي نمتلك الرؤية على الاستفادة منها في الوقت المناسب. وختاماً.. شكراً لكم، وأتمنى لكم منتدى ناجحاً ومثمراً، ولشراكتنا الإماراتية اللبنانية المزيد من التقدم والنجاح.
+متري
+ممثلاً رئيس مجلس الوزراء الدكتور نواف سلام الدكتور طارق متري قال في كلمته غنيّ عن القول إن رئيس الوزراء يرى في هذه الزيارة تعبيرًا عن استعادة الثقة بلبنان، أيًّا كانت من الصعاب التي تنتحلها . والصعاب كبيرة، لكن إرادتنا الوطنية كبيرة أيضًا، ومعها قدرة القوى الحية في لبنان على المثابرة وعلى النهوض.
+كلكم يعرف أن بلدنا شقّ طريقًا نحو استعادة سيادته، والطريق هذه وعرة، لذلك نحتاج إلى دعم أشقائنا العرب وأصدقائنا في العالم.
+واستعادة السيادة مزدوجة الهدف: وقف الحرب وإنهاء الاحتلال، والحفاظ على وحدة الأراضي اللبنانية وسلامتها من جهة أولى، ومن جهة ثانية بسط سلطة الدولة على أراضيها كافة، فتكون صاحبة القرار في الحرب والسلم دون سواها، وتمتلك حصرية السلاح.
+واستعادة السيادة متلازمة مع عودة المهجّرين إلى ديارهم، وتأمين شروط الحياة لهم، وإعادة بناء ما تهدّم. وهذا ما يرتّب على الدولة مسؤولية كبيرة في رعاية مواطنيها وحفظ أرواحهم وأرزاقهم، وتقديم العون لهم بلا تقاعس ولا منّة.
+أجدّد الترحيب بكم، وأدعو الله سبحانه وتعالى أن يكون الملتقى لا مساحة حوار بين أصدقاء ونظرائهم فحسب، بل أن يكون مدماكًا جديدًا قوي البنيان، تقوم عليه العلاقة الأخوية بين شعبينا الإماراتي واللبناني.
+لقد نُسجت خيوط هذه العلاقة منذ أيام المغفور له الشيخ زايد بن سلطان آل نهيان، طيّب الله ثراه، فهو الذي فتح أبواب الإمارات للأشقاء العرب، وفي مقدمهم اللبنانيون. فاستُضيفوا بأعداد متزايدة، وكانوا أوفياء للإمارات في كدّهم وفي البناء والتطوير.
+وباتت دولة الإمارات مقصد الصّفوة من خريجي جامعاتنا وأصحاب الخبرات في نواحي الاقتصاد والمعلوماتية والزراعة والصناعة. لذلك، ليس لقاء اليوم للتعرّف والتعارف، ولن يكون، بإذن الله، مجرد مناسبة عابرة، بل هو فرصة لتعزيز علاقات الثقة والتواصل والشراكة. فلبنان كان وما زال بلدًا منفتحًا، ومجتمعًا يمتلك طاقات بشرية غنية، وهو قادر على تحويل محدودية موارده إلى حافز للمعرفة والابتكار والمبادرة.
+أما دولة الإمارات العربية المتحدة، فقد باتت بمثابة نموذج فريد من نوعه في تحقيق نهضة استثنائية، وهي نهضة ملهمة في الرؤية وفي الفعل، في الطموح وفي النجاحات.
+لست بحاجة أن أتحدث أمامكم عن الإمكانات التي تفتحها الشراكة بين بلدينا، وبخاصة بين رجال الأعمال وسيداتها. فأنتم أطول باعًا مني في السعي الدؤوب وراء جلب المنافع ودرء المفاسد، لكنني أثق بأن مجيئكم إلينا هو شهادة لمحبتكم ولإيمانكم بأن اللبنانيين قادرون على النهوض، أيًّا كانت قساوة الأيام. وقد بيّنوا ذلك مرة بعد مرة. ولا يخفى على أحد منا أن الدولة اللبنانية، بمؤسساتها كافة، مدعوة أن تستحق ثقتكم كما ثقة اللبنانيين، وهذا واجبها وديدنها. إن أولى مسؤوليات حكومتنا هيًئ تعزيز مؤسسات الدولة عن طريق إصلاحها، وترسيخ سيادة القانون، وإعادة الانتظام المالي، وتحسين بيئة الأعمال، وتطوير البنى التحتية، وتوفير فرص العمل من خلال تشجيع الاستثمارات.
+المزروعي
+أما وكيل دائرة التنمية الاقتصادية – أبوظبي حمد صياح المزروعي فقال ورسالتنا لهم واضحة: لا تنظروا إلى أبوظبي كسوق فقط.انظروا إليها كمنصة، منصة تستطيعون من خلالها تأسيس أعمالكم، والوصول إلى رأس المال، وبناء الشراكات، والتوسع إلى أسواق المنطقة والعالم.
+وفي أبوظبي اليوم منظومة من القطاعات الواعدة تشمل الصناعة المتقدمة، والذكاء الاصطناعي والتكنولوجيا، والتجارة والخدمات اللوجستية، والطاقة النظيفة، والرعاية الصحية وعلوم الحياة، والأمن الغذائي والمائي، والسياحة والصناعات الإبداعية، والخدمات المالية.
+فالشراكة الحقيقية لا تكون في اتجاه واحد.
+وكما نرحب بالشركات والكفاءات اللبنانية في أبوظبي، فإننا نتطلع أيضاً إلى مرحلة جديدة من التعاون تتيح للشركات والمستثمرين الإماراتيين المشاركة في الفرص الاقتصادية الواعدة في لبنان.
+لبنان يمتلك رأس مال بشري متميزاً، وقطاعاً خاصاً يتمتع بروح المبادرة، وموقعاً استراتيجياً، وقدرات اقتصادية يمكن البناء عليها.
+ونرى مجالات واعدة للتعاون والاستثمار في البنية التحتية والخدمات اللوجستية، والطاقة والطاقة المتجددة، والتحول الرقمي والتكنولوجيا، والأمن الغذائي والصناعات الغذائية، والسياحة والضيافة، والرعاية الصحية، والخدمات المالية.
+وما نطمح إليه هو بناء شراكات إماراتية – لبنانية طويلة الأمد تجمع بين رأس المال والخبرة والقدرات في البلدين، وتنقل علاقاتنا الاقتصادية إلى مستوى جديد من التكامل والمنفعة المشتركة.
+وأعتقد أن دورنا كحكومات واضح: أن نفتح الأبواب.أن نزيل العوائق.أن نسهل ممارسة الأعمال.وأن نبني الثقة.
+أما الاستثمارات والشراكات والمشاريع الحقيقية، فيصنعها مجتمع الأعمال في بلدينا.
+لذلك، أتمنى ألا نغادر هذا المنتدى اليوم بالأفكار والنوايا فقط.
+نريد أن نخرج منه بفرص واضحة، وشراكات جديدة، ومشاريع قابلة للتنفيذ.
+وأن تكون هذه الزيارة بداية مرحلة اقتصادية جديدة بين الإمارات ولبنان، تقوم على الاستثمار والمواهب والابتكار والمصالح المشتركة. ختاماً، أتقدم بخالص الشكر والتقدير لحسن الاستقبال وكرم الضيافة، متمنياً للجمهورية اللبنانية الشقيقة وشعبها الكريم دوام الأمن والاستقرار والتقدم والازدهار.
+بوعميم
+من جهته، ألقى رئيس مجلس الاعمال اللبناني الاماراتي عن الجانب الإماراتي حمد بوعميم كلمة قال فيها الآتي: العلاقة بين لبنان ودولة الإمارات، وما تم التأكيد عليه بشأنها، وكذلك الفرص والإمكانيات المتاحة، كلها أمور مهمة. لكنني، بصفتي اليوم رئيس مجلس الأعمال الإماراتي اللبناني من الجانب الإماراتي، أود أن أركز على نقطة واحدة، وهي: ماذا سنفعل من هنا؟
+هذا الملتقى، بصراحة، يشكل إنجازًا، ونرى أن دولة الإمارات ولبنان، والحكومتين في البلدين، مهّدوا الطريق لوضع أسس قوية. واليوم ننتقل إلى دور المجلس ودور القطاع الخاص.
+أعتقد أن طموحنا من المجلس، بالتعاون طبعًا مع إخواننا في الجانب اللبناني، هو أن يكون مجلس عمل ونتائج، وليس فقط مجرد منصة للقاءات والحوارات.
+وهدفنا من خلال المجلس هو الربط بين رجال الأعمال والمستثمرين في البلدين، وتحديد الفرص بصورة واضحة وقابلة للتنفيذ، وتشجيع الشراكات والمشاريع التي تحدثنا عنها وتحويلها إلى واقع. وكذلك، العمل مع الجهات الحكومية والمعنية لتحديد التحديات، وإن شاء الله، العمل على حلها.
+كلنا نعرف اليوم أن رأس المال يحتاج إلى الثقة، والثقة تحتاج إلى إصلاح، وإن شاء الله مع عودة الثقة يعود رأس المال كذلك. وكما قال الإخوان، نحن لا نريد أن ننتظر إلى أن تُحل كل الأمور، بل نريد أن نبدأ من اليوم، لأننا على ثقة بأن الأمور، إن شاء الله، تتجه نحو الأفضل قريبًا.
+كما نريد للمجلس، مثلما قال أخي حمد، أن يكرّس علاقة تسير في اتجاهين: استثمارات إماراتية وفرص في لبنان، وفي الوقت نفسه مساعدة الشركات اللبنانية والكفاءات الموجودة على الاستفادة من دولة الإمارات كمنصة للوصول إلى العالم، لأننا بالفعل مهيّأون لذلك.
+إن نجاح المجلس، بإذن الله، لن يُقاس بعدد الاجتماعات واللقاءات، بل بعدد الفرص التي نستطيع تحويلها إلى شراكات ومشاريع فعلية.
+نحن متفائلون، إن شاء الله، بما يمكن تحقيقه، وطموحنا هو العمل مع زملائنا في الجانب اللبناني للوصول إلى نتائج ملموسة تخدم الطرفين.
+ضاهر
+وألقى رئيس مجلس الأعمال اللبناني الإماراتي وسيم ضاهر كلمة قال فيها الآتي:
+يسعدني أن أرحب بالوفد الاقتصادي الإماراتي الشقيق، برئاسة معالي الوزير الدكتور ثاني بن أحمد الزيودي في لبنان، وأن أعرب عن اعتزازنا بالعلاقات التاريخية التي تجمع بين بلدينا وشعبينا. لقد احتضنت دولة الإمارات اللبنانيين لعقود من الزمن، ووفرت لهم فرص العمل والنجاح والإبداع، فكانت لهم وطناً ثانياً ووجهة مفضلة للاستثمار والشراكة. وإننا نثمّن دعم الإمارات الدائم للبنان وحرصها على استقراره وازدهاره. وانطلاقاً من الثقة التي جمعت فخامة رئيسي البلدين، قامت غرفة بيروت وجبل لبنان برئاسة معالي الوزير محمد شقير، بتشكيل مجلس الأعمال اللبناني–الإماراتي، ويضم نخبة من رجال الأعمال اللبنانيين ذوي الخبرة والعلاقات الراسخة في دولة الإمارات. وقد تقرر تشكيل المجلس، ليكون منصة عملية لتعزيز التعاون وتبادل الخبرات وفتح آفاق جديدة أمام القطاع الخاص. ونحن نتطلع اليوم إلى الانتقال من التنسيق إلى شراكات ومشاريع واستثمارات متبادلة، وبناء تعاون استراتيجي طويل الأمد يستفيد من إمكانات البلدين وخبراتهما. وفي الختام، أتوجه بالشكر إلى دولة الإمارات الشقيقة، قيادة وشعباً، متمنياً لها دوام التقدم والريادة والازدهار، وللبنان الاستقرار والنهوض والازدهار
+العريس
+ثم ألقى رئيس إتحاد مجالس الأعمال اللبنانية الخليجية كلمة قال فيها الآتي:
+يفتح لبنان ذراعيه لاستقبالكم أنتم الذين لم تبخلوا يومًا بمحبتكم وعطائكم لبلدنا لبنان. نحن في اتحاد مجالس الأعمال اللبنانية الخليجية نضع في صلب أهدافنا العمل على تنمية العلاقات الاقتصادية بين لبنان ودول الخليج العربي الشقيقة، من خلال إطلاق برامج ومبادرات للتشبيك بين القطاع الخاص اللبناني ونظيره الخليجي، ولا سيما في المشاريع الكبرى التي تنفذها دول الخليج، بما يساهم في الحفاظ على الدور المهم الذي طالما اضطلع به القطاع الخاص اللبناني، وعلى مدى قرون، في هذه الدول الشقيقة، وتطوير هذا الدور بما يتلاءم مع الفرص الاقتصادية والاستثمارية الجديدة. كما نعمل على تأمين انخراط القطاع الخاص الخليجي في المشاريع والاستثمارات المطروحة في لبنان، في القطاعين العام والخاص، بما يعزز الشراكة الاقتصادية بين الجانبين، ويفتح آفاقًا جديدة للتعاون والاستثمار، ويحوّل العلاقات المميزة التي تجمع لبنان ودول الخليج إلى شراكات اقتصادية مستدامة ومثمرة للطرفين. ونحن نقدّر عاليًا ما تمثله الدول الخليجية الشقيقة من حاضنة اقتصادية واجتماعية للبنان، وما قدمته وما تزال تقدمه من دعم ومساندة للبنان واللبنانيين. وفي هذا الإطار، نطّلع دولة الإمارات العربية المتحدة الشقيقة بدور متميز ومتقدم، وتشكل نموذجًا رائدًا في دعم العلاقات الإنسانية والاقتصادية مع لبنان، وفي بناء شراكات قائمة على الثقة والانفتاح والمصلحة المشتركة. لذلك نقول لكم اليوم: شكرًا على كل شيء، وشكرًا على محبتكم للبنان، وعلى حرصكم الدائم على تعزيز العلاقات بين بلدينا وشعبينا الشقيقين. ولنا أمل كبير في أن تشكل زيارتكم الوازنة، على مختلف المستويات، انطلاقة جديدة وواعدة للعلاقات الاقتصادية الإماراتية اللبنانية، وأن تفتح صفحة جديدة من التعاون والشراكة، وأن تتحول هذه الزيارة إلى فرص ومبادرات ومشاريع تعود بالنفع على اقتصاد بلدينا وشعبينا. أهلًا وسهلًا بكم مجددًا. الله يحمي الإمارات، والله يحمي لبنان.
+توقيع مذكرات تفاهم
+بعد انتهاء الكلمات جرى توقيع 5 مذكرات تفاهم بين الجانبين اللبناني والإماراتي
+* مذكرة تفاهم بين اتحاد غرف الامارات للتجارة والصناعة واتحاد الغرف اللبنانية لتأسيس مجلس أعمال لبناني إماراتي مشارك وقعها:
+-سعادة عبدالله سلطان العويس، نائب رئيس اتحاد غرف الامارات، رئيس غرفة تجارة وصناعه الشارقه.
+-معالي الاستاذ محمد شقير رئيس اتحاد الغرف اللبنانية ورئيس غرفة بيروت وجبل لبنان
+* مذكرة تفاهم بين غرفة التجارة والصناعة والزراعة في بيروت وجبل لبنان وبين غرفة تجارة وصناعة أبوظبي، وقعها:
+- سعادة الاستاذ علي بن حرمل الظاهري ، نائب الأول لرئيس غرفة أبوظبي
+- معالي الاستاذ محمد شقير رئيس غرفة بيروت وجبل لبنان
+* مذكرة تفاهم بين غرفة بيروت وجبل لبنان وغرفة رأس الخيمة وقعها:
+سعادة محمد علي النعيمي ، رئيس غرفة رأس الخيمة
+ومعالي الاستاذ محمد سقير رئيس غرفة بيروت وجبل لبنان
+*مذكرة تفاهم بين شركة ايليت اجرو القابضة والجامعة الاميركية في بيروت حول التعاون في الأمن الغذائي وأبحاث الزراعة الجافة والابتك بمشاركة وزير الزراعة الدكتور نزار هاني وقعها:
+الدكتور عماد بعلبكي وعمار علبي عن الجامعة الاميركية
+السيد حسن علاوي عن شركة أيليت آجرو.
+*مذكرة تفاهم بين شركة إيليت أجرو القابضة وشركة جرجي دكاش وأولاده المحدودة للتعاون في حلول البيوت المحمية: التصميم والتوريد والتركيب والتشغيل والصيانة، إضافة إلى الدعم الفني والتدريب والتطوير المشترك وقعها:
+سعادة النائب شوقي دكاش عن شركة جرجي دكاش
+السيد حسن علاوي عن شركة أيليت آجرو
+ثم جرى تبادل هدايا حيث قدم الوزير شقير هدايا لوزير التجارة الخارجية في الإمارات الدكتور ثاني بن أحمد الزيّودي ونائب رئيس اتحاد غرف الإمارات سلطان عبدالله العويس، كما قدم كل من الوزراء عامر البساط، وجو عيسى الخوري وكمال شحادة هدايا تذكارية . وبعدها قدم الوزير الزيودي لشقير والوزراء هدايا تذكارية.
+اجتماع مجلس الأعمال اللبناني المشترك
+وبعد توقيع مذكرة التفاهم وعلى أثر توقيع التفاهم بإنشاء مجلس الأعمال الإماراتي اللبناني المشترك، عقد المجلس اجتماعه الأول بمشاركة الوزير الدكتور ثاني بن أحمد الزيّودي والوزير السابق محمد شقير وترأسه عن الجانب الإماراتي د.حمد بوعميم وعن الجانب اللبناني وسيم ضاهر.
+جلسات عمل
+كذلك جرى عقد جلسات عمل الأولى تحت عنوان: الشراكة في مشاريع البنية التحتية وإعادة الإعمار: فرص الاستثمار والتعاون اللبناني – الإماراتي شارك فيها كل من رئيس مجلس إدارة مجلس الإنماء والإعمار محمد علي قباني، رئيس نقابة مقاولي الأشغال العامة والبناء في لبنان المهندس مارون الحلو، رئيس مجلس الإدارة شركة روتانا لإدارة الفنادق ناصر محمد ناصر النويس والرئيس التنفيذي لمجموعة سيراميك راس الخيمة عبدالله مسعد.
+أما الجلسة الحوارية الثانية بعنوان: " من الفرص إلى الشراكات الاستثمارية: آفاق الاستثمار اللبناني – الإماراتي ودور القطاع الخاص تحدث فيها كل من: رئيس مجلس إدارة المؤسسة العامة لتشجيع الاستثمارات في لبنان – IDAL ماجد منيمنة رئيس اتحاد المستثمرين اللبنانيين جاك صراف، رئيس مجلس الإدارة عيسى الغرير للاستثمار عيسى عبدالله الغرير والمدير التنفيذي للشؤون التجارية شركة دليل للتكنولوجيا محمد المازمي.</t>
+        </is>
+      </c>
+      <c r="E131" t="inlineStr">
+        <is>
+          <t>2026-10-29T11:21:48.068153+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" t="inlineStr">
+        <is>
+          <t>عيسى الخوري يحقّق مع معهد البحوث الصناعية لادخاله شحنة اسمنت من دون فحوصات وطلب اتّخاذ الاجراءات الق</t>
+        </is>
+      </c>
+      <c r="B132" t="inlineStr">
+        <is>
+          <t>http://www.industry.gov.lb/Media/News/عيسى-الخوري-يحقق-مع-معهد-البحوث-الصناعية-لادخاله-ش</t>
+        </is>
+      </c>
+      <c r="C132" t="inlineStr">
+        <is>
+          <t>2011-01-01</t>
+        </is>
+      </c>
+      <c r="D132" t="inlineStr">
+        <is>
+          <t>عيسى الخوري يحقّق مع معهد البحوث الصناعية لادخاله شحنة اسمنت من دون فحوصات وطلب اتّخاذ الاجراءات القانونيّة بحقّ المتقاعسين
+وجّه وزير الصناعة جو عيسى الخوري كتاباً إلى مدير عام معهد البحوث الصناعية "طلب فيه إجراء تحقيق فوري مع الموظفين المعنيّين بإدخال شحنة إسمنت عبر مرفأ طرابلس لصالح شركة دير عمار ميتال ش.م.م دون إخضاعها للفحوصات اللازمة لدى معهد البحوث الصناعية، وإتخاذ الإجراءات المناسبة بحقّهم."
+وإذ شدّد عيسى الخوري على "إيداعه كافة المستندات المتعلّقة بالملف ونتيجة التحقيق بالسرعة القصوى."
+وأضاف في كتابه:" لقد تبيّن أن الشحنة المذكورة تم إدخالها بناء على إفادة صادرة عن معهد البحوث الصناعية وموجّهة لإدارة الجمارك اللبنانية تفيد بأن "البضاعة غير خاضعة لأحكام المراسيم الإلزامية المكلف بتطبيقها و/أو لكونها بكميات إفرادية قليلة". علماً أنّه لا يمكن إدخال الإسمنت المستورد إلى السوق اللبناني إلا بعد الحصول على إفادة صادرة من معهد البحوث الصناعية بالموافقة، وذلك بموجب المرسوم رقم ٩٧٦٦ تاريخ ۲۰۰۳/۳/۱۱ (إعطاء صفة الإلزام للمواصفة القياسية اللبنانية رقم ٥٣ المتعلقة بالإسمنت). وكان مدير عام وزارة الصناعة أبلغ المديرية العامة للجمارك بموجب كتابه رقم ٢٠١٦/١٣٤٩ - ۲۱٥ ص تاريخ ۲۰۲٦/٧/١٥ بذلك. ولما كان عمل معهد البحوث الصناعية يتعارض مع المراسيم المرعية ويخالف تعليمات وزارة الصناعة ويمكن أن يتسبّب بمخاطر كبيرة خاصة لجهة السلامة العامة في الأبنية والإنشاءات في حال عدم مطابقة الشحنة للمواصفات، طلب الوزير عيسى الخوري من معهد البحوث الصناعية سحب الإفادة المذكورة وإبلاغ المديرية العامة للجمارك بقرار السحب وعدم العمل بها".</t>
+        </is>
+      </c>
+      <c r="E132" t="inlineStr">
+        <is>
+          <t>2026-10-29T11:21:50.659289+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" t="inlineStr">
+        <is>
+          <t>عيسى الخوري من قصر بعبدا "نقف الى جانب الرئيس في مسألة اتفاق الاطار والقطاع الصناعي يحتاج الى استثم</t>
+        </is>
+      </c>
+      <c r="B133" t="inlineStr">
+        <is>
+          <t>http://www.industry.gov.lb/Media/News/عيسى-الخوري-من-قصر-بعبدا-نقف-الى-جانب-الرييس-في-مس</t>
+        </is>
+      </c>
+      <c r="C133" t="inlineStr">
+        <is>
+          <t>2011-01-01</t>
+        </is>
+      </c>
+      <c r="D133" t="inlineStr">
+        <is>
+          <t>عيسى الخوري من قصر بعبدا "نقف الى جانب الرئيس في مسألة اتفاق الاطار والقطاع الصناعي يحتاج الى استثمارات ومواصفات الانتاج ممتازة"
+تابع رئيس الجمهورية
+العماد جوزاف عون مع وزير الصناعة جو عيسى الخوري، اوضاع الوزارة والجهود التي يقوم بها لمساعدة الصناعيين اللبنانيين.
+وبعد اللقاء، قال الوزير عيسى الخوري:
+"اطلعت فخامة الرئيس خلال اللقاء على الملفات التي تتابعها وزارة الصناعة، وتحدثنا عن الوضع الاقتصادي العام والصناعي تحديداً. واكدت لفخامة الرئيس اننا نقف الى جانبه في مسألة اتفاق الاطار الذي يتابعه، ولا يحق لاحد ان يزايد عليه في ما يقوم به او يشك في لبنانيته او وطنيته. وفّق الله فخامة الرئيس وحماه."
+سئل: هل ابلغكم فخامة الرئيس عن موعد لجولة مقبلة في المفاوضات؟
+اجاب: لا اعلم بعد ما اذا تقرر موعد نهائي للجولة المقبلة.
+سئل: هل من جديد في مواضيع الصناعة والمساعدات او دعم للبنان؟
+اجاب: دائماً ما اميّز بين القطاعين العام والخاص، فمن اسس ازدهار لبنان تاريخياً هو القطاع الخاص، واليوم هناك ازمة تطاول بشكل اكبر القطاع العام الذي يحتاج الى المساعدة، اما القطاع الخاص فلا يحتاج الى مساعدة بل الى استثمارات وهذا ما نحاول ايصاله لاصدقاء لبنان وللبنانيين في الخارج. في مجال الصناعة، هناك شق صناعي تقليدي وهناك الصناعات التكنولوجية التي نسعى الى تسويقها خارج لبنان.
+سئل: ماذا عن العقبات التي تواجه الصادرات اللبنانية الى السعودية والخليج؟
+اجاب: ما قامت به الحكومة في الفترة الاخيرة منذ حوالي السنة ونصف السنة، ذللت فيه عقبات كثيرة تقارب نسبتها الـ95 في المئة، ونحن في صدد اعادة التصدير بشكل سليم وسريع الى السعودية وكافة البلدان. اما الاشكالية فتتعلق بكلفة الانتاج بالنسبة الى الصناعيين، لان الصناعي اللبناني، وللاسف، يدفع اعلى كلفة كيلواط/ ساعة في العالم ويبلغ كمعدل بحدود 31-32 سنتا بينما في تركيا مثلاً هو 5.4 وفي مصر 4.2 و في الخليج واوروبا اقل بكثير مما هو عليه في لبنان، فالصناعي اللبناني لا ينافس لبنانياً آخر، بل اي منتج يدخل الى لبنان ومعظم المنتجات تكون مدعومة من الدول، وعلينا النظر في كيفية مساعدة الصناعيين اللبنانيين لمنافسة الصناعات التي ترد من الخارج.
+سئل: هل المواصفات جيدة؟
+اجاب: بل ممتازة، فنوعية الانتاج اللبناني وجودته في السنوات الاربع الاخيرة، تطوّرا بشكل جيد، وهناك المجلس اللبناني للاعتماد "كوليباك" الذي سيعطي الاعتماد للمختبرات والمؤسسات التي تصدر شهادات "ايزو" للتأكيد على جودة الانتاج اللبناني بما يساعد اكثر على التصدير</t>
+        </is>
+      </c>
+      <c r="E133" t="inlineStr">
+        <is>
+          <t>2026-10-29T11:21:53.271407+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" t="inlineStr">
+        <is>
+          <t>عيسى الخوري افتتح ورشة عمل في الاسكوا عن ادماج المشاريع الصغيرة والمتوسطة في الاقتصاد الدائري " لن ي</t>
+        </is>
+      </c>
+      <c r="B134" t="inlineStr">
+        <is>
+          <t>http://www.industry.gov.lb/Media/News/عيسى-الخوري-افتتح-ورشة-عمل-في-الاسكوا-عن-ادماج-الم</t>
+        </is>
+      </c>
+      <c r="C134" t="inlineStr">
+        <is>
+          <t>2011-01-01</t>
+        </is>
+      </c>
+      <c r="D134" t="inlineStr">
+        <is>
+          <t>عيسى الخوري افتتح ورشة عمل في الاسكوا عن ادماج المشاريع الصغيرة والمتوسطة في الاقتصاد الدائري " لن يتحقق ما لم يكن مجدياً للمؤسسات الصناعية"
+افتتح وزير الصناعة جو عيسى الخوري قبل ظهر اليوم ورشة عمل عن "بناء القدرات لصانعي السياسات في لبنان حول ادماج المشاريع الصغيرة والمتوسطة في الاقتصاد الدائري وتطوير السياسات،" في مقرّ اللجنة الاقتصادية والاجتماعية لغربي آسيا (الاسكوا). وتنظّم الورشة التي تستمرّ ثلاثة أيام، وزارة الصناعة بالتعاون مع المنظّمة الدولية. وشارك المدير العام لوزارة الصناعة عادل الشباب، كبار المسؤولين في الاسكوا والوزارات والادارات والقطاع الخاص.
+وألقى الوزير عيسى الخوري كلمة اقترح فيها " وضع خارطة طريق وطنية نلتزم بالعمل عليها عبر مسارات ثلاثة متوازية:المسار الأول هو الاطار التنظيمي، من خلال إعداد برنامج مبسّط ومتدرّج يتلاءم مع واقع المشاريع الصغيرة والمتوسطة، يشمل تعريفاً واضحاً للمواد المعاد تدويرها، وتبسيط التراخيص، وإنشاء نقطة اتصال موحدة داخل الوزارة لمواكبة هذا التحول. وما ستعلنونه من توصيات وأطر تنظيمية سيكون جزءاً أساسياً من هذه العملية.
+"أما المسار الثاني فهو الحوافز والتمويل، لأن التحوّل الدائري لن يتحقق ما لم يكن مجدياً اقتصادياً للمؤسسات الصناعية نفسها. لذلك سنعمل مع شركائنا على تطوير حزمة متكاملة تشمل تحسين فرص الوصول إلى التمويل الأخضر، ودراسة الحوافز الضريبية، وتعزيز المشتريات العامة المستدامة، بما يشجع الاستثمار في الإنتاج الأنظف والابتكار.
+"والمسار الثالث هو التنفيذ القطاعي التجريبي، من خلال إطلاق مبادرات رائدة في قطاعات نرى فيها فرص نجاح واعدة وكبيرة وفي مقدمتها الصناعات الغذائية، والتغليف والبلاستيك، ومواد البناء، لتكون نماذج عملية تثبت أن الاقتصاد الدائري ليس مجرد مفهوم نظري، بل فرصة حقيقية للنمو الصناعي وخلق القيمة المضافة."</t>
+        </is>
+      </c>
+      <c r="E134" t="inlineStr">
+        <is>
+          <t>2026-10-29T11:21:55.854874+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" t="inlineStr">
+        <is>
+          <t>ماغرو ودّع عيسى الخوري</t>
+        </is>
+      </c>
+      <c r="B135" t="inlineStr">
+        <is>
+          <t>http://www.industry.gov.lb/Media/News/ماغرو-ودع-عيسى-الخوري</t>
+        </is>
+      </c>
+      <c r="C135" t="inlineStr">
+        <is>
+          <t>2011-01-01</t>
+        </is>
+      </c>
+      <c r="D135" t="inlineStr">
+        <is>
+          <t>ماغرو ودّع عيسى الخوري
+استقبل وزير الصناعة جو عيسى الخوري سفير فرنسا في لبنان هيرفيه ماغرو في زيارة وداعية، أكدا فيها على عمق العلاقات اللبنانية - الفرنسية، وتطوير آفاق التعاون الصناعي خاصة في مجال الصناعات التكنولوجية بين البلدين.
+وكانت مناسبة شكر فيها الوزير عيسى الخوري السفير ماغرو على الجهود التي قام بها لمساعدة القطاعين العام والخاص لتخطي الصعوبات التي يمر فيها لبنان.</t>
+        </is>
+      </c>
+      <c r="E135" t="inlineStr">
+        <is>
+          <t>2026-10-29T11:21:58.339515+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" t="inlineStr">
+        <is>
+          <t>عيسى الخوري استقبل القائم بالأعمال الليبي</t>
+        </is>
+      </c>
+      <c r="B136" t="inlineStr">
+        <is>
+          <t>http://www.industry.gov.lb/Media/News/عيسى-الخوري-استقبل-القايم-بالاعمال-الليبي</t>
+        </is>
+      </c>
+      <c r="C136" t="inlineStr">
+        <is>
+          <t>2011-01-01</t>
+        </is>
+      </c>
+      <c r="D136" t="inlineStr">
+        <is>
+          <t>10 تموز 2026 عيسى الخوري استقبل القائم بالأعمال الليبي استقبل وزير الصناعة جو عيسى الخوري سفير دولة ليبيا لدى سوريا والقائم بالأعمال في لبنان وليد حسن محمد عمار، وبحثا في أهمية تعزيز العلاقات بين لبنان وليبيا وتطوير الاستثمار الصناعي بين البلدين.</t>
+        </is>
+      </c>
+      <c r="E136" t="inlineStr">
+        <is>
+          <t>2026-10-29T11:22:00.996136+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" t="inlineStr">
+        <is>
+          <t>عيسى الخوري عزّى سفير فنزويلا "لابقاء الترابط مع الجاليات فعال وديناميكي"</t>
+        </is>
+      </c>
+      <c r="B137" t="inlineStr">
+        <is>
+          <t>http://www.industry.gov.lb/Media/News/عيسى-الخوري-عزى-سفير-فنزويلا-لابقاء-الترابط-مع-الج</t>
+        </is>
+      </c>
+      <c r="C137" t="inlineStr">
+        <is>
+          <t>2011-01-01</t>
+        </is>
+      </c>
+      <c r="D137" t="inlineStr">
+        <is>
+          <t>عيسى الخوري عزّى سفير فنزويلا "لابقاء الترابط مع الجاليات فعال وديناميكي"
+بحث وزير الصناعة جو عيسى الخوري مع سفير فنزويلا لدى لبنان خوسيه غريغوريو بيومورجي في لقاء جمعهما في الوزارة، في سبل تعزيز التعاون والتبادل التجاري والصناعي بين لبنان وفنزويلا.
+وتطرقا الى العلاقات بين البلدين. وقدّم عيسى الخوري تعازيه الى السفير بضحايا الزلزال الذي ضرب بلاده، وتمنى له أن تتجاوز هذه المحنة والخسائر.
+وأكد السفير للوزير ان اللبنانيين في فنزويلا يبلغون نصف مليون شخص تقريباً، ويشكلون جالية مندمجة مع بيئتها ومجتمعها، ويعمل أبناؤها في أنشطة متعددة، ويساهمون في بناء البلاد على صعد عدة.
+وتوافق الوزير والسفير على ضرورة تفعيل دورهم على صعيد تثبيت العلاقة مع وطنهم الأم وبناء جسور تفاعل اقتصادي وصناعي واجتماعي تبقي روابط الاغتراب مع لبنان قائمة وديناميكية.</t>
+        </is>
+      </c>
+      <c r="E137" t="inlineStr">
+        <is>
+          <t>2026-10-29T11:22:03.565960+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" t="inlineStr">
+        <is>
+          <t>عيسى الخوري ثمّن الثقة السعودية المتجدّدة بالصناعة اللبنانية</t>
+        </is>
+      </c>
+      <c r="B138" t="inlineStr">
+        <is>
+          <t>http://www.industry.gov.lb/Media/News/عيسى-الخوري-ثمن-الثقة-السعودية-المتجددة-بالصناعة-ا</t>
+        </is>
+      </c>
+      <c r="C138" t="inlineStr">
+        <is>
+          <t>2011-01-01</t>
+        </is>
+      </c>
+      <c r="D138" t="inlineStr">
+        <is>
+          <t>عيسى الخوري ثمّن الثقة السعودية المتجدّدة بالصناعة اللبنانية
+استقبل وزير الصناعة جو عيسى الخوري سفير المملكة العربية السعودية لدى لبنان، فهد بن عبد الرحمن الدوسري في مكتبه بالوزارة، وبحثا في سبل تعزيز العلاقات والتعاون بين لبنان والمملكة على الصعد الاقتصادية والصناعية، لا سيما في ضوء القرار السعودي الأخير بالسماح بدخول المنتجات اللبنانية الصناعية والزراعية الى المملكة السعودية.
+وأكد عيسى الخوري أن هذا القرار يشكل محطة مفصلية للصناعة اللبنانية، لما يحمله من دعم مباشر للاقتصاد الوطني، ويفتح الباب أمام تعزيز الصادرات اللبنانية الى دول الخليج. وطمأن السفير الى أن جودة الصناعات اللبنانية ممتازة، والصناعيين اللبنانيين توّاقون للعودة بناء على الثقة المتجدّدة بهم في المملكة.</t>
+        </is>
+      </c>
+      <c r="E138" t="inlineStr">
+        <is>
+          <t>2026-10-29T11:22:06.137368+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" t="inlineStr">
+        <is>
+          <t>حفل العشاء الختامي لبرنامج "Lebanon Innovate"</t>
+        </is>
+      </c>
+      <c r="B139" t="inlineStr">
+        <is>
+          <t>http://www.industry.gov.lb/Media/News/حفل-العشاء-الختامي-لبرنامج-Lebanon-Innovate</t>
+        </is>
+      </c>
+      <c r="C139" t="inlineStr">
+        <is>
+          <t>2011-01-01</t>
+        </is>
+      </c>
+      <c r="D139" t="inlineStr">
+        <is>
+          <t>حفل العشاء الختامي لبرنامج "Lebanon Innovate"
+أكد وزير الصناعة جو عيسى الخوري في حفل العشاء الختامي لبرنامج "Lebanon Innovate" الذي يموّله الاتحاد الأوروبي بقيادة بيريتيك، أننا نعيش تحوّلات جيوسياسيّة وتكنولوجيّة عميقة، تتطلّب دعم البحث العلمي الذي لم يعد ترفًا أكاديميًا أو نشاطًا نظريًا مجردًا، بل حاجة ماسّة للتطوير والتحديث الصناعي وريادة الأعمال والابتكار.
+واعتبر ان الصناعة التكنولوجية اللبنانية قادرة على المنافسة لتمتّع العاملين فيها بالمرونة والذكاء والابداع، وهم يشكّلون الموارد البشريّة التي تُميّز لبنان عن الكثير من البلدان.
+وتابع: "الابتكار والجودة والسمعة هم وسيلتنا التسويقيّة الرئيسيّة،ساعين مع الصناعيّين الى نقل البحث العلمي من الدراسات إلى خطوط الإنتاج، وتحويل المعرفة إلى منتجات، والأفكار إلى صناعات، والابتكار إلى قيمة اقتصادية وفرص عمل."
+وشدد عيسى الخوري على ان هذا التوجّه يتطلّب بناء جسر مؤسّسي ومستدام بين الجامعات والقطاع الصناعي، وتحويل الأبحاث إلى نتائج ملموسة تعزّز قدرتنا التنافسيّة في الأسواق العالميّة.
+ودعا وزير الصناعة إلى إطلاق الميثاق الوطني للمعرفة، ليكون في خدمة لبنان وصناعته الوطنية، ويرتكز على إنشاء هيئة وطنية للابتكار، إقرار حوافز ضريبية للبحث والتطوير، تعزيز التواصل مع الكفاءات اللبنانية المنتشرة في العالم، إنشاء تجمّعات متخصّصة للبحث والتطوير في القطاعات التي يتمتّع فيها لبنان بميزات تنافسيّة حقيقية وإقامة شراكة دائمة ومستدامة بين الجامعات والقطاع الصناعي والعلماء والباحثين والمهندسين اللبنانيين المنتشرين في أبرز الجامعات ومراكز الأبحاث العالمية</t>
+        </is>
+      </c>
+      <c r="E139" t="inlineStr">
+        <is>
+          <t>2026-10-29T11:22:08.718766+00:00</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Ministry_of_Industry.xlsx
+++ b/Ministry_of_Industry.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E139"/>
+  <dimension ref="A1:E140"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
   <cols>
     <col width="45" customWidth="1" min="1" max="1"/>
@@ -5876,6 +5876,39 @@
         </is>
       </c>
     </row>
+    <row r="140">
+      <c r="A140" t="inlineStr">
+        <is>
+          <t>تُطلق وزارة الصناعة، بدعم من برنامج الأمم المتحدة الإنمائي (UNDP) وبتمويل من حكومة كندا، منصة رقمية</t>
+        </is>
+      </c>
+      <c r="B140" t="inlineStr">
+        <is>
+          <t>http://www.industry.gov.lb/Media/News/تطلق-وزارة-الصناعة،-بدعم-من-برنامج-الامم-المتحدة-ا</t>
+        </is>
+      </c>
+      <c r="C140" t="inlineStr">
+        <is>
+          <t>2026-10-29</t>
+        </is>
+      </c>
+      <c r="D140" t="inlineStr">
+        <is>
+          <t>تُطلق وزارة الصناعة، بدعم من برنامج الأمم المتحدة الإنمائي (UNDP) وبتمويل من حكومة كندا، منصة رقمية جديدة للخدمات الصناعية.
+يمكنكم الآن التقدّم بطلب الترخيص و الشهادة الصناعية إلكترونياً، ومتابعة آخر المستجدات المتعلقة بطلبكم، والوصول إلى جميع الخدمات ذات الصلة عبر منصة رقمية موحّدة.
+تساهم هذه المبادرة في تحديث الخدمات الصناعية في لبنان، من خلال تسهيل الإجراءات وجعلها أكثر سرعةً وشفافيةً وسهولةً الاستخدام.
+The Ministry of Industry, with the support of UNDP and generous funding from the Government of Canada, is launching a new digital platform for industrial services.
+You can now apply for industrial permits and certificates online, track the status of your applications, and access all related services through a single digital platform.
+This initiative modernizes industrial service delivery in Lebanon by making procedures faster, more transparent, and easier to access.
+اضغط هنا للاطلاع على المنصة الرقمية للحصول على التراخيص والشهادات الصناعية</t>
+        </is>
+      </c>
+      <c r="E140" t="inlineStr">
+        <is>
+          <t>2026-10-30T11:25:11.369645+00:00</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
